--- a/public/hormonizacion-centros.xlsx
+++ b/public/hormonizacion-centros.xlsx
@@ -15877,10 +15877,10 @@
         <v>1530</v>
       </c>
       <c r="H332">
-        <v>-31.500853</v>
+        <v>-31.53628593911067</v>
       </c>
       <c r="I332">
-        <v>-68.5404772</v>
+        <v>-68.53760571366831</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">

--- a/public/hormonizacion-centros.xlsx
+++ b/public/hormonizacion-centros.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="1944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="1944">
   <si>
     <t>nombre</t>
   </si>
@@ -3847,7 +3847,7 @@
     <t>Formosa</t>
   </si>
   <si>
-    <t>Padre Patiño y Salta</t>
+    <t>Ing. L. Huergo y A. O. Daugero</t>
   </si>
   <si>
     <t>(370) 443-1323</t>
@@ -3886,7 +3886,7 @@
     <t>(370) 444-5561</t>
   </si>
   <si>
-    <t>Hospital Manuel Belgrano</t>
+    <t>Hospital General Manuel Belgrano</t>
   </si>
   <si>
     <t>Jujuy</t>
@@ -3895,13 +3895,13 @@
     <t>Humahuaca</t>
   </si>
   <si>
-    <t>Santa Fe 34</t>
+    <t>Santa Fe 34 (esq. Tierra del Fuego)</t>
   </si>
   <si>
     <t>(3887) 42-1009</t>
   </si>
   <si>
-    <t>Hospital Maimará</t>
+    <t>Hospital de Maimará Dr. Miguel Ángel Miskoff</t>
   </si>
   <si>
     <t>Maimará</t>
@@ -3919,13 +3919,13 @@
     <t>Palpalá</t>
   </si>
   <si>
-    <t>Av. Quispe (esq. Chacho Peñaloza)</t>
+    <t>Cabo Quispe y Chacho Peñaloza</t>
   </si>
   <si>
     <t>(388) 427-5996</t>
   </si>
   <si>
-    <t>Hospital Dr. Guillermo Paterson</t>
+    <t>Hospital Dr. Guillermo C. Paterson</t>
   </si>
   <si>
     <t>Hormonización, Atención a Infancias, Ginecología</t>
@@ -3982,22 +3982,22 @@
     <t>General Pico</t>
   </si>
   <si>
-    <t>Calle 17 Oeste 500-598</t>
+    <t>25 de Mayo S/N (entre Calle 112 y Calle 110)</t>
   </si>
   <si>
     <t>(2302) 43-6148</t>
   </si>
   <si>
-    <t>Establecimiento Asistencial Dr. Manuel Freire</t>
+    <t>Hospital Dr. Manuel Freire</t>
   </si>
   <si>
     <t>Guatraché</t>
   </si>
   <si>
-    <t>1° Junta 158</t>
-  </si>
-  <si>
-    <t>(2954) 49-2532</t>
+    <t>Primera Junta 158</t>
+  </si>
+  <si>
+    <t>(2954) 49-2532 / 49-2035</t>
   </si>
   <si>
     <t>Hospital Dr. Lucio Molas</t>
@@ -4009,16 +4009,19 @@
     <t>Raúl B. Díaz y Pilcomayo</t>
   </si>
   <si>
-    <t>(2954) 455-000 (int. 3216)</t>
+    <t>(2954) 455-000 (int. 3216) / 38-3700</t>
   </si>
   <si>
     <t>Hospital Luisa Pedemonte de Pistarini</t>
   </si>
   <si>
+    <t>Hormonización, Atención a Infancias, Salud Mental</t>
+  </si>
+  <si>
     <t>Victorica</t>
   </si>
   <si>
-    <t>Calle 21, 1194</t>
+    <t>Calle 15 S/N (entre Calle 26 y Calle 28)</t>
   </si>
   <si>
     <t>(2954) 49-7489</t>
@@ -4030,9 +4033,6 @@
     <t>Hospital Regional Dr. Enrique Vera Barros</t>
   </si>
   <si>
-    <t>Atención a Infancias, Atención Integral</t>
-  </si>
-  <si>
     <t>La Rioja</t>
   </si>
   <si>
@@ -4042,7 +4042,7 @@
     <t>Olta y Madre Teresa de Calcuta</t>
   </si>
   <si>
-    <t>0800-444-0211</t>
+    <t>0800-444-0211 / (380) 442-7782 / 445-3552</t>
   </si>
   <si>
     <t>servicio_adolescencia_larioja@yahoo.com.ar</t>
@@ -4051,7 +4051,7 @@
     <t>Centro de Atención Primaria de Salud (CAPS) La Cañada y Anexo Parque de la Familia</t>
   </si>
   <si>
-    <t>Proyectada y Faustino Molina</t>
+    <t>Faustino Molina S/N (entre Enrique Quique Neira y Jorge Agüero)</t>
   </si>
   <si>
     <t>(380) 436-9421</t>
@@ -4090,7 +4090,7 @@
     <t>modosi.comunicacion@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Dr. Humberto Notti</t>
+    <t>Hospital Pediátrico Dr. Humberto Notti</t>
   </si>
   <si>
     <t>Guaymallén</t>
@@ -4105,7 +4105,7 @@
     <t>saludmentalnotti@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Central</t>
+    <t>Hospital Central de Mendoza</t>
   </si>
   <si>
     <t>Hormonización, Atención a Infancias, Salud Mental, Cirugía de Masculinización Tórax, Grupo de Pares</t>
@@ -4114,7 +4114,7 @@
     <t>Alem 450</t>
   </si>
   <si>
-    <t>(261) 449-0684</t>
+    <t>(261) 449-0684 / 385-5509</t>
   </si>
   <si>
     <t>Hospital Teodoro J. Schestakow</t>
@@ -4135,13 +4135,13 @@
     <t>trabajosocialschestakow@gmail.com</t>
   </si>
   <si>
-    <t>Centro de Atención Primaria de Salud (CAPS) N°198 Fermín Carrizo - La Arboleda</t>
+    <t>Centro de Atención Primaria de Salud (CAPS) N°198 Fermín Carrizo</t>
   </si>
   <si>
     <t>Tupungato</t>
   </si>
   <si>
-    <t>Calle Iriarte S/N</t>
+    <t>Calle Iriarte S/N, La Arboleda</t>
   </si>
   <si>
     <t>(2622) 48-9153</t>
@@ -4180,7 +4180,7 @@
     <t>(376) 475-5550</t>
   </si>
   <si>
-    <t>Hospital de Itaembé Guazú</t>
+    <t>Hospital de Itaembé de Guazú</t>
   </si>
   <si>
     <t>Atención a Infancias, Endocrinología, Ginecología, Trabajo Social</t>
@@ -4195,16 +4195,16 @@
     <t>msp_itaembeguazu@misiones.gov.ar</t>
   </si>
   <si>
-    <t>Hospital Nuestra Señora de Fátima</t>
-  </si>
-  <si>
-    <t>Calle 3 y 13</t>
+    <t>Hospital Vírgen de Fátima</t>
+  </si>
+  <si>
+    <t>Av. Jorge Kemerer y Melchora</t>
   </si>
   <si>
     <t>(376) 440-9118</t>
   </si>
   <si>
-    <t>Centro de Salud 15 de Febrero</t>
+    <t>Centro de Salud Comunitario 15 de Febrero</t>
   </si>
   <si>
     <t>Neuquén</t>
@@ -4213,19 +4213,16 @@
     <t>Junín de los Andes</t>
   </si>
   <si>
-    <t>Patagonia 540</t>
-  </si>
-  <si>
-    <t>(294) 591-6213</t>
+    <t>Patagonia 567</t>
+  </si>
+  <si>
+    <t>(294) 591-6213 / 41-9042</t>
   </si>
   <si>
     <t>Centro de Salud Barrio Lanín</t>
   </si>
   <si>
-    <t>Hormonización, Atención a Infancias, Salud Mental</t>
-  </si>
-  <si>
-    <t>Río Negro S/N</t>
+    <t>Río Negro 350</t>
   </si>
   <si>
     <t>(2972) 49-1208</t>
@@ -4234,13 +4231,13 @@
     <t>Centro de Salud Barrio Lonquimay</t>
   </si>
   <si>
-    <t>Gines Ponte 343</t>
+    <t>Laura Vicuña 380</t>
   </si>
   <si>
     <t>(294) 15-458-5213</t>
   </si>
   <si>
-    <t>Hospital Loncopué Dr. José Enrique Cuevas</t>
+    <t>Hospital de Área Loncopué Dr. José Enrique Cuevas</t>
   </si>
   <si>
     <t>Loncopué</t>
@@ -4264,13 +4261,13 @@
     <t>rondaencuentros@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Bouquet Roldan</t>
-  </si>
-  <si>
-    <t>Teodoro Planas 1915</t>
-  </si>
-  <si>
-    <t>(299) 464-5782</t>
+    <t>Hospital de Área Bouquet Roldan</t>
+  </si>
+  <si>
+    <t>Dr. Luis Teodoro Planas 1915</t>
+  </si>
+  <si>
+    <t>(299) 464-5782 / 443-8183</t>
   </si>
   <si>
     <t>Hospital Dr. Horacio Heller</t>
@@ -4303,7 +4300,7 @@
     <t>equipoextension.subse@gmail.com</t>
   </si>
   <si>
-    <t>Centro de Salud Los Aromos</t>
+    <t>Centro de Salud Barrio Los Aromos</t>
   </si>
   <si>
     <t>Plottier</t>
@@ -4315,16 +4312,16 @@
     <t>(299) 493-7203</t>
   </si>
   <si>
-    <t>Hospital de Plottier</t>
-  </si>
-  <si>
-    <t>Sargento Cabral y Paraguay</t>
+    <t>Hospital de Área Plottier</t>
+  </si>
+  <si>
+    <t>Sargento Cabral y Lacar</t>
   </si>
   <si>
     <t>(299) 493-6098</t>
   </si>
   <si>
-    <t>Centro de Salud Tiro Federal Ida China Paredes</t>
+    <t>Centro de Salud B° Tiro Federal Ida China Paredes</t>
   </si>
   <si>
     <t>San Martín de los Andes</t>
@@ -4339,7 +4336,7 @@
     <t>equidiversidadsma@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Regional Ramón Carrillo</t>
+    <t>Hospital Regional Dr. Ramón Carrillo</t>
   </si>
   <si>
     <t>Pasaje del Pueblo 247</t>
@@ -4351,7 +4348,7 @@
     <t>equipodiversidadsma@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Adolfo del Valle Senillosa</t>
+    <t>Hospital de Área Adolfo del Valle</t>
   </si>
   <si>
     <t>Hormonización, Atención a Infancias, Salud Mental, Grupo de Pares</t>
@@ -4360,16 +4357,16 @@
     <t>Senillosa</t>
   </si>
   <si>
-    <t>Belgrano y Neuquén</t>
-  </si>
-  <si>
-    <t>(299) 689-4212</t>
+    <t>Av. Belgrano y Neuquén</t>
+  </si>
+  <si>
+    <t>(299) 689-4212 / 492-0626</t>
   </si>
   <si>
     <t>adolescencia.hospitalsenillosa@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Dr. Oscar Arraiz</t>
+    <t>Hospital de Área Dr. Oscar Arraiz</t>
   </si>
   <si>
     <t>Villa La Angostura</t>
@@ -4384,27 +4381,12 @@
     <t>consultoriointegraldiversovla@gmail.com</t>
   </si>
   <si>
-    <t>Consultorio LGBTIQ+ Allen</t>
+    <t>Hospital de Área Dra. Cecilia Grierson</t>
   </si>
   <si>
     <t>Río Negro</t>
   </si>
   <si>
-    <t>Allen</t>
-  </si>
-  <si>
-    <t>Quesnel S/N</t>
-  </si>
-  <si>
-    <t>(2984) 760-683</t>
-  </si>
-  <si>
-    <t>consultorioamigable.lgbtiq@gmail.com</t>
-  </si>
-  <si>
-    <t>Hospital Dra. Cecilia Grierson</t>
-  </si>
-  <si>
     <t>Catriel</t>
   </si>
   <si>
@@ -4414,7 +4396,7 @@
     <t>(299) 654-7362</t>
   </si>
   <si>
-    <t>Hospital Área Programa Dr. Pedro Moguillansky - Consultorio Inclusivo Claudia Pía Baudracco</t>
+    <t>Hospital de Área Programa Dr. Pedro Moguillansky - Consultorio Inclusivo Claudia Pía Baudracco</t>
   </si>
   <si>
     <t>Cipolletti</t>
@@ -4453,10 +4435,10 @@
     <t>General Roca</t>
   </si>
   <si>
-    <t>Gelonch 721</t>
-  </si>
-  <si>
-    <t>(2984) 165-557</t>
+    <t>Eduardo Gelonch 721</t>
+  </si>
+  <si>
+    <t>(2984) 165-557 / 43-5852</t>
   </si>
   <si>
     <t>Centro de Salud de Barrio El Rosario</t>
@@ -4468,6 +4450,12 @@
     <t>Eliseo Calegari 1250</t>
   </si>
   <si>
+    <t>(2931) 432-600 / 432-222 / 421-982</t>
+  </si>
+  <si>
+    <t>hospitalriocolorado@hotmail.com</t>
+  </si>
+  <si>
     <t>Hospital Zonal Ramón Carrillo</t>
   </si>
   <si>
@@ -4486,13 +4474,13 @@
     <t>adolescenciasbariloche@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Dr. Elías Smirnoff</t>
+    <t>Hospital de Área Dr. Elías Smirnoff</t>
   </si>
   <si>
     <t>Villa Regina</t>
   </si>
   <si>
-    <t>Fray Luis Beltrán 496</t>
+    <t>Fray Luis Beltrán 476</t>
   </si>
   <si>
     <t>(298) 446-1277</t>
@@ -4510,10 +4498,13 @@
     <t>12 de Octubre (esq. Costanera)</t>
   </si>
   <si>
+    <t>(3868) 42-2011</t>
+  </si>
+  <si>
     <t>nadua144@hotmail.com</t>
   </si>
   <si>
-    <t>Centro de Salud Manjón</t>
+    <t>Centro de Salud N°6 El Manjón</t>
   </si>
   <si>
     <t>Av. José de Artigas 902</t>
@@ -4528,10 +4519,10 @@
     <t>Hormonización, Atención a Infancias, Ginecología, Clínica Médica</t>
   </si>
   <si>
-    <t>Sarmiento 655</t>
-  </si>
-  <si>
-    <t>(387) 442-7152 / 431-9349 / 421-3387 / 431-7400 / 0800-777-6452</t>
+    <t>Av. Sarmiento 655</t>
+  </si>
+  <si>
+    <t>(387) 431-9349 / 442-7152 / 421-3387 / 431-7400 / 0800-777-6452</t>
   </si>
   <si>
     <t>hsmcapacitacion@gmail.com</t>
@@ -4540,7 +4531,10 @@
     <t>Hospital Dr. Arturo Oñativia - Consultorio de Diversidad</t>
   </si>
   <si>
-    <t>Paz Chaín 30</t>
+    <t>E. Paz Chaín 30</t>
+  </si>
+  <si>
+    <t>(387) 422-1605</t>
   </si>
   <si>
     <t>Centro de Atención Primaria de Salud (CAPS) Villa Constitución</t>
@@ -4570,25 +4564,19 @@
     <t>Av. Guillermo Rawson Sur 494</t>
   </si>
   <si>
-    <t>(264) 621-0689</t>
-  </si>
-  <si>
-    <t>Hospital Público Dr.Marcial Quiroga</t>
+    <t>(264) 621-0689 / 422-4005</t>
+  </si>
+  <si>
+    <t>Hospital Público Dr. Marcial Vicente Quiroga</t>
   </si>
   <si>
     <t>Av. Libertador Gral. San Martín 5401</t>
   </si>
   <si>
-    <t>Ministerio de Salud de la Provincia</t>
-  </si>
-  <si>
-    <t>Av. Libertador y Calle Las Heras</t>
-  </si>
-  <si>
-    <t>(264) 430-6981</t>
-  </si>
-  <si>
-    <t>iniciativamildias@gmail.com</t>
+    <t>(264) 432-4700</t>
+  </si>
+  <si>
+    <t>hospitalmarcialquirogasanjuan@gmail.com</t>
   </si>
   <si>
     <t>Centro de Adiestramiento Dr. René Favaloro (CARF) La Rotonda - Consultorio de Diversidad y Salud Sexual</t>
@@ -4660,7 +4648,7 @@
     <t>La Punta</t>
   </si>
   <si>
-    <t>5 Sur entre 8 Este y Av. Serrana</t>
+    <t>Calle 5 Sur (entre Calle 8 Este y Av. Serrana)</t>
   </si>
   <si>
     <t>(266) 445-2000 (int. 5002)</t>
@@ -4669,7 +4657,7 @@
     <t>adolescenciasanluis@gmail.com</t>
   </si>
   <si>
-    <t>Centro de Salud Los Molles</t>
+    <t>Centro de Salud N°56 Los Molles</t>
   </si>
   <si>
     <t>Los Molles</t>
@@ -4684,7 +4672,10 @@
     <t>Hospital Madre Catalina Rodríguez</t>
   </si>
   <si>
-    <t>Ruta 1 y El Ceibo</t>
+    <t>Ruta 1 y Bv. El Ceibo</t>
+  </si>
+  <si>
+    <t>(2656) 47-3712 / (2664) 17-5949 / 83-6675</t>
   </si>
   <si>
     <t>Centro de Salud Papagayos</t>
@@ -4705,13 +4696,16 @@
     <t>Marcelino Poblet 668</t>
   </si>
   <si>
+    <t>(266) 461-0695</t>
+  </si>
+  <si>
     <t>adolescenciassanluis@gmail.com</t>
   </si>
   <si>
     <t>Centro de Atención Primaria de Salud (CAPS) N°9 San Gerónimo</t>
   </si>
   <si>
-    <t>San Gerónimo S/N</t>
+    <t>San Gerónimo y Diagonal Sainz</t>
   </si>
   <si>
     <t>(2656) 473-712 / (2664) 175-949</t>
@@ -4744,13 +4738,16 @@
     <t>(2954) 51-0037</t>
   </si>
   <si>
-    <t>Hospital Suárez Rocha</t>
+    <t>hospitalunion2018@gmail.com</t>
+  </si>
+  <si>
+    <t>Hospital del Sur Dr. Justo Suárez Rocha</t>
   </si>
   <si>
     <t>Villa Mercedes</t>
   </si>
   <si>
-    <t>Héctor Aubert S/N</t>
+    <t>Héctor Aubert S/N (entre Capitan Bolzan y Tiburcia Escudero)</t>
   </si>
   <si>
     <t>Hospital de Alta Complejidad SAMIC El Calafate</t>
@@ -4771,16 +4768,16 @@
     <t>derechosysalud.samic@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Distrital Gobernador Gregores</t>
+    <t>Hospital Distrital de Gobernador Gregores Dr. Ramón Eraso Santa Paul</t>
   </si>
   <si>
     <t>Gobernador Gregores</t>
   </si>
   <si>
-    <t>Mario Paradelo 1025</t>
-  </si>
-  <si>
-    <t>(2966) 589-694</t>
+    <t>Mario C. Paradelo 1025</t>
+  </si>
+  <si>
+    <t>(2966) 589-694 / (2962) 49-1027</t>
   </si>
   <si>
     <t>Hospital Distrital Las Heras</t>
@@ -4789,10 +4786,13 @@
     <t>Las Heras</t>
   </si>
   <si>
-    <t>28 de Noviembre 315</t>
-  </si>
-  <si>
-    <t>(2974) 093-328</t>
+    <t>28 de Noviembre 315 (entre Juan José Paso y Juan Larrea)</t>
+  </si>
+  <si>
+    <t>(2974) 093-328 / 497-4666 / 497-6106</t>
+  </si>
+  <si>
+    <t>hdlhsalud@hotmail.com</t>
   </si>
   <si>
     <t>Sistema para la Atención Médica de la Comunidad (SAMCo) de Acebal - Hospital Ma. Saa Pereyra</t>
@@ -5611,7 +5611,7 @@
     <t>Aristóbulo del Valle 1699</t>
   </si>
   <si>
-    <t>(385) 416-2701 / 600-6879 / 627-9845</t>
+    <t>(385) 416-2701 / 600-6879 / 627-9845 / 427-5784</t>
   </si>
   <si>
     <t>Centro Provincial de Salud Infantil (CEPSI)</t>
@@ -5629,7 +5629,7 @@
     <t>serviciosaludsexualcepsi@gmail.com / comunicacioninstitucional@cepsi.gob.ar</t>
   </si>
   <si>
-    <t>Hospital Independencia</t>
+    <t>Hospital Zonal Independencia</t>
   </si>
   <si>
     <t>Hormonización, Atención a Infancias, Clínica Médica, Trabajo Social</t>
@@ -5647,7 +5647,7 @@
     <t>Unidad de Pronta Atención (UPA) N°25 Barrio Belén</t>
   </si>
   <si>
-    <t>Manzana 14 S/N, Barrio Belén</t>
+    <t>Nazareth S/N, Manzana 14 Barrio Belén</t>
   </si>
   <si>
     <t>(385) 068-440 / 473-7984 / 477-8640</t>
@@ -5689,7 +5689,7 @@
     <t>(2964) 43-6223 (int. 6065) / 44-3074</t>
   </si>
   <si>
-    <t>Centro de Atención Primaria de Salud (CAPS) N°3 - Consultorio de Diversidad Nicolás Cristal</t>
+    <t>Centro de Atención Primaria de Salud (CAPS) N°3 Dr. Tomas Gonzalez - Consultorio de Diversidad Nicolás Cristal</t>
   </si>
   <si>
     <t>Endocrinología, Salud Mental, Clínica Médica, Trabajo Social</t>
@@ -5758,7 +5758,7 @@
     <t>consultoriodediversidadushuaia@gmail.com / capstressalud@gmail.com</t>
   </si>
   <si>
-    <t>Hospital Regional de Ushuaia - Gobernador Ernesto Campos</t>
+    <t>Hospital Regional de Ushuaia - Gobernador Ernesto Manuel Campos</t>
   </si>
   <si>
     <t>12 de Octubre y Maipú</t>
@@ -6230,7 +6230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I430"/>
+  <dimension ref="A1:I428"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
@@ -14154,10 +14154,10 @@
         <v>61</v>
       </c>
       <c r="H273">
-        <v>-26.1878096</v>
+        <v>-26.19981747992999</v>
       </c>
       <c r="I273">
-        <v>-58.168051</v>
+        <v>-58.1517846632507</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -14270,10 +14270,10 @@
         <v>61</v>
       </c>
       <c r="H277">
-        <v>-23.204098</v>
+        <v>-23.200919800279113</v>
       </c>
       <c r="I277">
-        <v>-65.3495159</v>
+        <v>-65.3504464262738</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -14299,10 +14299,10 @@
         <v>61</v>
       </c>
       <c r="H278">
-        <v>-23.6236374</v>
+        <v>-23.631267090399792</v>
       </c>
       <c r="I278">
-        <v>-65.407168</v>
+        <v>-65.41135371639416</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -14328,10 +14328,10 @@
         <v>61</v>
       </c>
       <c r="H279">
-        <v>-24.2537486</v>
+        <v>-24.253809081861448</v>
       </c>
       <c r="I279">
-        <v>-65.21004</v>
+        <v>-65.20865548929592</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
@@ -14357,10 +14357,10 @@
         <v>61</v>
       </c>
       <c r="H280">
-        <v>-24.2374226</v>
+        <v>-24.234200238087286</v>
       </c>
       <c r="I280">
-        <v>-64.8737578</v>
+        <v>-64.8719092032402</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -14473,10 +14473,10 @@
         <v>61</v>
       </c>
       <c r="H284">
-        <v>-35.6695045</v>
+        <v>-35.6724740442987</v>
       </c>
       <c r="I284">
-        <v>-63.7638034</v>
+        <v>-63.7664587285339</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -14502,10 +14502,10 @@
         <v>61</v>
       </c>
       <c r="H285">
-        <v>-37.6665306</v>
+        <v>-37.66527562662069</v>
       </c>
       <c r="I285">
-        <v>-63.547478</v>
+        <v>-63.547627360552326</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -14531,10 +14531,10 @@
         <v>61</v>
       </c>
       <c r="H286">
-        <v>-36.6119823</v>
+        <v>-36.59861315727386</v>
       </c>
       <c r="I286">
-        <v>-64.2898299</v>
+        <v>-64.29067864122727</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -14542,36 +14542,36 @@
         <v>1333</v>
       </c>
       <c r="B287" t="s">
-        <v>710</v>
+        <v>1334</v>
       </c>
       <c r="C287" t="s">
         <v>1321</v>
       </c>
       <c r="D287" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E287" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="F287" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="G287" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H287">
-        <v>-36.2217989</v>
+        <v>-36.22102952764992</v>
       </c>
       <c r="I287">
-        <v>-65.4353775</v>
+        <v>-65.43101935033256</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B288" t="s">
-        <v>1339</v>
+        <v>10</v>
       </c>
       <c r="C288" t="s">
         <v>1340</v>
@@ -14600,7 +14600,7 @@
         <v>1345</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>46</v>
       </c>
       <c r="C289" t="s">
         <v>1340</v>
@@ -14618,10 +14618,10 @@
         <v>1348</v>
       </c>
       <c r="H289">
-        <v>-29.4177103</v>
+        <v>-29.463696899349948</v>
       </c>
       <c r="I289">
-        <v>-66.9094128</v>
+        <v>-66.86678345958971</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -14629,7 +14629,7 @@
         <v>1349</v>
       </c>
       <c r="B290" t="s">
-        <v>710</v>
+        <v>1334</v>
       </c>
       <c r="C290" t="s">
         <v>1350</v>
@@ -14658,7 +14658,7 @@
         <v>1355</v>
       </c>
       <c r="B291" t="s">
-        <v>929</v>
+        <v>536</v>
       </c>
       <c r="C291" t="s">
         <v>1350</v>
@@ -14676,10 +14676,10 @@
         <v>1358</v>
       </c>
       <c r="H291">
-        <v>-32.9152166</v>
+        <v>-32.91612545114127</v>
       </c>
       <c r="I291">
-        <v>-68.8665768</v>
+        <v>-68.86726180840485</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -14734,10 +14734,10 @@
         <v>61</v>
       </c>
       <c r="H293">
-        <v>-34.9727832</v>
+        <v>-32.892193291381176</v>
       </c>
       <c r="I293">
-        <v>-67.7038567</v>
+        <v>-68.83287464356341</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -14792,10 +14792,10 @@
         <v>1378</v>
       </c>
       <c r="H295">
-        <v>-33.37311183383466</v>
+        <v>-33.37311230614287</v>
       </c>
       <c r="I295">
-        <v>-69.11268540768205</v>
+        <v>-69.11268273087582</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -14850,10 +14850,10 @@
         <v>61</v>
       </c>
       <c r="H297">
-        <v>-27.3751781</v>
+        <v>-27.375360543074574</v>
       </c>
       <c r="I297">
-        <v>-55.9384677</v>
+        <v>-55.9374292800899</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -14879,10 +14879,10 @@
         <v>1393</v>
       </c>
       <c r="H298">
-        <v>-27.4103422</v>
+        <v>-27.4101123465621</v>
       </c>
       <c r="I298">
-        <v>-55.9838383</v>
+        <v>-55.98375076608754</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -14908,10 +14908,10 @@
         <v>61</v>
       </c>
       <c r="H299">
-        <v>-27.4258774</v>
+        <v>-27.43639999771612</v>
       </c>
       <c r="I299">
-        <v>-55.9428605</v>
+        <v>-55.86960458400177</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -14937,10 +14937,10 @@
         <v>61</v>
       </c>
       <c r="H300">
-        <v>-39.9471653</v>
+        <v>-39.948079428993765</v>
       </c>
       <c r="I300">
-        <v>-71.0696598</v>
+        <v>-71.06667034269567</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -14948,7 +14948,7 @@
         <v>1402</v>
       </c>
       <c r="B301" t="s">
-        <v>1403</v>
+        <v>1334</v>
       </c>
       <c r="C301" t="s">
         <v>1398</v>
@@ -14957,27 +14957,27 @@
         <v>1399</v>
       </c>
       <c r="E301" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F301" t="s">
         <v>1404</v>
-      </c>
-      <c r="F301" t="s">
-        <v>1405</v>
       </c>
       <c r="G301" t="s">
         <v>61</v>
       </c>
       <c r="H301">
-        <v>-39.940965</v>
+        <v>-39.9408056188762</v>
       </c>
       <c r="I301">
-        <v>-71.0664334</v>
+        <v>-71.06727699873093</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B302" t="s">
-        <v>1403</v>
+        <v>1334</v>
       </c>
       <c r="C302" t="s">
         <v>1398</v>
@@ -14986,24 +14986,24 @@
         <v>1399</v>
       </c>
       <c r="E302" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F302" t="s">
         <v>1407</v>
-      </c>
-      <c r="F302" t="s">
-        <v>1408</v>
       </c>
       <c r="G302" t="s">
         <v>61</v>
       </c>
       <c r="H302">
-        <v>-39.9536258</v>
+        <v>-39.953405339736406</v>
       </c>
       <c r="I302">
-        <v>-71.066076</v>
+        <v>-71.07142253768743</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B303" t="s">
         <v>287</v>
@@ -15012,13 +15012,13 @@
         <v>1398</v>
       </c>
       <c r="D303" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E303" t="s">
         <v>1410</v>
       </c>
-      <c r="E303" t="s">
+      <c r="F303" t="s">
         <v>1411</v>
-      </c>
-      <c r="F303" t="s">
-        <v>1412</v>
       </c>
       <c r="G303" t="s">
         <v>61</v>
@@ -15032,10 +15032,10 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B304" t="s">
         <v>1413</v>
-      </c>
-      <c r="B304" t="s">
-        <v>1414</v>
       </c>
       <c r="C304" t="s">
         <v>1398</v>
@@ -15044,27 +15044,27 @@
         <v>1398</v>
       </c>
       <c r="E304" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F304" t="s">
         <v>61</v>
       </c>
       <c r="G304" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H304">
-        <v>-40.1323252</v>
+        <v>-38.949289914093804</v>
       </c>
       <c r="I304">
-        <v>-71.2952414</v>
+        <v>-68.0560455873368</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B305" t="s">
-        <v>586</v>
+        <v>57</v>
       </c>
       <c r="C305" t="s">
         <v>1398</v>
@@ -15073,27 +15073,27 @@
         <v>1398</v>
       </c>
       <c r="E305" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F305" t="s">
         <v>1418</v>
-      </c>
-      <c r="F305" t="s">
-        <v>1419</v>
       </c>
       <c r="G305" t="s">
         <v>61</v>
       </c>
       <c r="H305">
-        <v>-38.9590528</v>
+        <v>-38.95899954453859</v>
       </c>
       <c r="I305">
-        <v>-68.0711585</v>
+        <v>-68.08586645129849</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B306" t="s">
-        <v>287</v>
+        <v>46</v>
       </c>
       <c r="C306" t="s">
         <v>1398</v>
@@ -15102,13 +15102,13 @@
         <v>1398</v>
       </c>
       <c r="E306" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F306" t="s">
         <v>61</v>
       </c>
       <c r="G306" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H306">
         <v>-38.93701702412</v>
@@ -15119,7 +15119,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B307" t="s">
         <v>938</v>
@@ -15131,24 +15131,24 @@
         <v>1398</v>
       </c>
       <c r="E307" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F307" t="s">
         <v>61</v>
       </c>
       <c r="G307" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H307">
-        <v>-38.9512963</v>
+        <v>-38.9511998563012</v>
       </c>
       <c r="I307">
-        <v>-68.0577221</v>
+        <v>-68.057813385052</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B308" t="s">
         <v>979</v>
@@ -15160,24 +15160,24 @@
         <v>1398</v>
       </c>
       <c r="E308" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F308" t="s">
         <v>1427</v>
       </c>
-      <c r="F308" t="s">
+      <c r="G308" t="s">
         <v>1428</v>
       </c>
-      <c r="G308" t="s">
-        <v>1429</v>
-      </c>
       <c r="H308">
-        <v>-38.9447674</v>
+        <v>-38.951862884667456</v>
       </c>
       <c r="I308">
-        <v>-68.0506462</v>
+        <v>-68.05074439086091</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B309" t="s">
         <v>57</v>
@@ -15186,27 +15186,27 @@
         <v>1398</v>
       </c>
       <c r="D309" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E309" t="s">
         <v>1431</v>
       </c>
-      <c r="E309" t="s">
+      <c r="F309" t="s">
         <v>1432</v>
-      </c>
-      <c r="F309" t="s">
-        <v>1433</v>
       </c>
       <c r="G309" t="s">
         <v>61</v>
       </c>
       <c r="H309">
-        <v>-38.9587083</v>
+        <v>-38.95860258532684</v>
       </c>
       <c r="I309">
-        <v>-68.2406404</v>
+        <v>-68.24167287687207</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B310" t="s">
         <v>57</v>
@@ -15215,56 +15215,56 @@
         <v>1398</v>
       </c>
       <c r="D310" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E310" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F310" t="s">
         <v>1435</v>
-      </c>
-      <c r="F310" t="s">
-        <v>1436</v>
       </c>
       <c r="G310" t="s">
         <v>61</v>
       </c>
       <c r="H310">
-        <v>-38.9483117</v>
+        <v>-38.948942161225325</v>
       </c>
       <c r="I310">
-        <v>-68.226839</v>
+        <v>-68.22873901064094</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B311" t="s">
-        <v>1403</v>
+        <v>1334</v>
       </c>
       <c r="C311" t="s">
         <v>1398</v>
       </c>
       <c r="D311" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E311" t="s">
         <v>1438</v>
       </c>
-      <c r="E311" t="s">
+      <c r="F311" t="s">
         <v>1439</v>
       </c>
-      <c r="F311" t="s">
+      <c r="G311" t="s">
         <v>1440</v>
       </c>
-      <c r="G311" t="s">
-        <v>1441</v>
-      </c>
       <c r="H311">
-        <v>-40.1594537</v>
+        <v>-40.150263729435174</v>
       </c>
       <c r="I311">
-        <v>-71.3511387</v>
+        <v>-71.35595648373196</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B312" t="s">
         <v>46</v>
@@ -15273,56 +15273,56 @@
         <v>1398</v>
       </c>
       <c r="D312" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E312" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F312" t="s">
         <v>1443</v>
       </c>
-      <c r="F312" t="s">
+      <c r="G312" t="s">
         <v>1444</v>
       </c>
-      <c r="G312" t="s">
-        <v>1445</v>
-      </c>
       <c r="H312">
-        <v>-40.148339</v>
+        <v>-40.14838174600873</v>
       </c>
       <c r="I312">
-        <v>-71.3270148</v>
+        <v>-71.32891669257668</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B313" t="s">
         <v>1446</v>
-      </c>
-      <c r="B313" t="s">
-        <v>1447</v>
       </c>
       <c r="C313" t="s">
         <v>1398</v>
       </c>
       <c r="D313" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E313" t="s">
         <v>1448</v>
       </c>
-      <c r="E313" t="s">
+      <c r="F313" t="s">
         <v>1449</v>
       </c>
-      <c r="F313" t="s">
+      <c r="G313" t="s">
         <v>1450</v>
       </c>
-      <c r="G313" t="s">
-        <v>1451</v>
-      </c>
       <c r="H313">
-        <v>-39.014747</v>
+        <v>-39.013617897381465</v>
       </c>
       <c r="I313">
-        <v>-68.4362261</v>
+        <v>-68.42591095532015</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B314" t="s">
         <v>1053</v>
@@ -15331,91 +15331,91 @@
         <v>1398</v>
       </c>
       <c r="D314" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E314" t="s">
         <v>1453</v>
       </c>
-      <c r="E314" t="s">
+      <c r="F314" t="s">
         <v>1454</v>
       </c>
-      <c r="F314" t="s">
+      <c r="G314" t="s">
         <v>1455</v>
       </c>
-      <c r="G314" t="s">
-        <v>1456</v>
-      </c>
       <c r="H314">
-        <v>-40.7793223</v>
+        <v>-40.77123584764593</v>
       </c>
       <c r="I314">
-        <v>-71.6555632</v>
+        <v>-71.65044019942675</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B315" t="s">
+        <v>46</v>
+      </c>
+      <c r="C315" t="s">
         <v>1457</v>
       </c>
-      <c r="B315" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C315" t="s">
+      <c r="D315" t="s">
         <v>1458</v>
       </c>
-      <c r="D315" t="s">
+      <c r="E315" t="s">
         <v>1459</v>
       </c>
-      <c r="E315" t="s">
+      <c r="F315" t="s">
         <v>1460</v>
       </c>
-      <c r="F315" t="s">
-        <v>1461</v>
-      </c>
       <c r="G315" t="s">
-        <v>1462</v>
+        <v>61</v>
       </c>
       <c r="H315">
-        <v>-38.9791554</v>
+        <v>-37.86238</v>
       </c>
       <c r="I315">
-        <v>-67.8197652</v>
+        <v>-67.7907657</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B316" t="s">
+        <v>241</v>
+      </c>
+      <c r="C316" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E316" t="s">
         <v>1463</v>
       </c>
-      <c r="B316" t="s">
-        <v>46</v>
-      </c>
-      <c r="C316" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D316" t="s">
+      <c r="F316" t="s">
         <v>1464</v>
       </c>
-      <c r="E316" t="s">
+      <c r="G316" t="s">
         <v>1465</v>
       </c>
-      <c r="F316" t="s">
-        <v>1466</v>
-      </c>
-      <c r="G316" t="s">
-        <v>61</v>
-      </c>
       <c r="H316">
-        <v>-37.86238</v>
+        <v>-38.9419376</v>
       </c>
       <c r="I316">
-        <v>-67.7907657</v>
+        <v>-67.9918495</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B317" t="s">
         <v>1467</v>
       </c>
-      <c r="B317" t="s">
-        <v>241</v>
-      </c>
       <c r="C317" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D317" t="s">
         <v>1468</v>
@@ -15430,10 +15430,10 @@
         <v>1471</v>
       </c>
       <c r="H317">
-        <v>-38.9419376</v>
+        <v>-41.95909957968307</v>
       </c>
       <c r="I317">
-        <v>-67.9918495</v>
+        <v>-71.542176943775</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
@@ -15441,68 +15441,68 @@
         <v>1472</v>
       </c>
       <c r="B318" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C318" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D318" t="s">
         <v>1473</v>
       </c>
-      <c r="C318" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D318" t="s">
+      <c r="E318" t="s">
         <v>1474</v>
       </c>
-      <c r="E318" t="s">
+      <c r="F318" t="s">
         <v>1475</v>
       </c>
-      <c r="F318" t="s">
-        <v>1476</v>
-      </c>
       <c r="G318" t="s">
-        <v>1477</v>
+        <v>61</v>
       </c>
       <c r="H318">
-        <v>-41.9579886</v>
+        <v>-39.02216724503028</v>
       </c>
       <c r="I318">
-        <v>-71.541808</v>
+        <v>-67.57339996259417</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E319" t="s">
         <v>1478</v>
       </c>
-      <c r="B319" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C319" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D319" t="s">
+      <c r="F319" t="s">
         <v>1479</v>
       </c>
-      <c r="E319" t="s">
+      <c r="G319" t="s">
         <v>1480</v>
       </c>
-      <c r="F319" t="s">
-        <v>1481</v>
-      </c>
-      <c r="G319" t="s">
-        <v>61</v>
-      </c>
       <c r="H319">
-        <v>-39.0185769</v>
+        <v>-38.98345731068331</v>
       </c>
       <c r="I319">
-        <v>-67.5947534</v>
+        <v>-64.10908586259357</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B320" t="s">
         <v>1482</v>
       </c>
-      <c r="B320" t="s">
-        <v>1403</v>
-      </c>
       <c r="C320" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D320" t="s">
         <v>1483</v>
@@ -15511,45 +15511,45 @@
         <v>1484</v>
       </c>
       <c r="F320" t="s">
-        <v>61</v>
+        <v>1485</v>
       </c>
       <c r="G320" t="s">
-        <v>61</v>
+        <v>1486</v>
       </c>
       <c r="H320">
-        <v>-38.91010267358859</v>
+        <v>-41.1362058</v>
       </c>
       <c r="I320">
-        <v>-67.98244730438678</v>
+        <v>-71.3001011</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B321" t="s">
-        <v>1486</v>
+        <v>57</v>
       </c>
       <c r="C321" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D321" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E321" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="F321" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="G321" t="s">
-        <v>1490</v>
+        <v>61</v>
       </c>
       <c r="H321">
-        <v>-41.1362058</v>
+        <v>-39.102103109844506</v>
       </c>
       <c r="I321">
-        <v>-71.3001011</v>
+        <v>-67.0846440304501</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
@@ -15557,57 +15557,57 @@
         <v>1491</v>
       </c>
       <c r="B322" t="s">
-        <v>57</v>
+        <v>1334</v>
       </c>
       <c r="C322" t="s">
-        <v>1458</v>
+        <v>1492</v>
       </c>
       <c r="D322" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="E322" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="F322" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="G322" t="s">
-        <v>61</v>
+        <v>1496</v>
       </c>
       <c r="H322">
-        <v>-39.1015629</v>
+        <v>-26.064866542973213</v>
       </c>
       <c r="I322">
-        <v>-67.0846347</v>
+        <v>-65.9829546133699</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B323" t="s">
-        <v>1403</v>
+        <v>586</v>
       </c>
       <c r="C323" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="D323" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="E323" t="s">
         <v>1498</v>
       </c>
       <c r="F323" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G323" t="s">
         <v>61</v>
       </c>
-      <c r="G323" t="s">
-        <v>1499</v>
-      </c>
       <c r="H323">
-        <v>-26.0673322</v>
+        <v>-24.80965000249162</v>
       </c>
       <c r="I323">
-        <v>-65.983162</v>
+        <v>-65.38198075333513</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
@@ -15615,57 +15615,57 @@
         <v>1500</v>
       </c>
       <c r="B324" t="s">
-        <v>586</v>
+        <v>1501</v>
       </c>
       <c r="C324" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="D324" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E324" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="F324" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="G324" t="s">
-        <v>61</v>
+        <v>1504</v>
       </c>
       <c r="H324">
-        <v>-24.8100006</v>
+        <v>-24.7814706</v>
       </c>
       <c r="I324">
-        <v>-65.3803152</v>
+        <v>-65.4158763</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B325" t="s">
-        <v>1504</v>
+        <v>57</v>
       </c>
       <c r="C325" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="D325" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E325" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="F325" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="G325" t="s">
-        <v>1507</v>
+        <v>61</v>
       </c>
       <c r="H325">
-        <v>-24.7814706</v>
+        <v>-24.789623811993685</v>
       </c>
       <c r="I325">
-        <v>-65.4158763</v>
+        <v>-65.39847193507809</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
@@ -15673,671 +15673,671 @@
         <v>1508</v>
       </c>
       <c r="B326" t="s">
-        <v>57</v>
+        <v>710</v>
       </c>
       <c r="C326" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="D326" t="s">
-        <v>1496</v>
+        <v>1510</v>
       </c>
       <c r="E326" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="F326" t="s">
-        <v>61</v>
+        <v>1512</v>
       </c>
       <c r="G326" t="s">
-        <v>61</v>
+        <v>1513</v>
       </c>
       <c r="H326">
-        <v>-24.7883597</v>
+        <v>-31.5913181</v>
       </c>
       <c r="I326">
-        <v>-65.3989494</v>
+        <v>-68.5530919</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="B327" t="s">
-        <v>710</v>
+        <v>1515</v>
       </c>
       <c r="C327" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D327" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="E327" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="F327" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="G327" t="s">
-        <v>1515</v>
+        <v>61</v>
       </c>
       <c r="H327">
-        <v>-31.5913181</v>
+        <v>-31.539413986242632</v>
       </c>
       <c r="I327">
-        <v>-68.5530919</v>
+        <v>-68.51322286243567</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B328" t="s">
-        <v>1517</v>
+        <v>586</v>
       </c>
       <c r="C328" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D328" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="E328" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="F328" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="G328" t="s">
-        <v>61</v>
+        <v>1521</v>
       </c>
       <c r="H328">
-        <v>-31.5216111</v>
+        <v>-31.530056615152713</v>
       </c>
       <c r="I328">
-        <v>-68.5165964</v>
+        <v>-68.59582530140682</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B329" t="s">
-        <v>586</v>
+        <v>1523</v>
       </c>
       <c r="C329" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D329" t="s">
-        <v>1511</v>
+        <v>1524</v>
       </c>
       <c r="E329" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="F329" t="s">
-        <v>61</v>
+        <v>1526</v>
       </c>
       <c r="G329" t="s">
-        <v>61</v>
+        <v>1527</v>
       </c>
       <c r="H329">
-        <v>-31.530056615152713</v>
+        <v>-31.573125352740586</v>
       </c>
       <c r="I329">
-        <v>-68.59582530140682</v>
+        <v>-68.52816662490439</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="B330" t="s">
-        <v>287</v>
+        <v>57</v>
       </c>
       <c r="C330" t="s">
-        <v>1511</v>
+        <v>1529</v>
       </c>
       <c r="D330" t="s">
-        <v>1511</v>
+        <v>1530</v>
       </c>
       <c r="E330" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="F330" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="G330" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="H330">
-        <v>-31.53628593911067</v>
+        <v>-32.41054142124651</v>
       </c>
       <c r="I330">
-        <v>-68.53760571366831</v>
+        <v>-65.01157990558708</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="B331" t="s">
-        <v>1527</v>
+        <v>57</v>
       </c>
       <c r="C331" t="s">
-        <v>1511</v>
+        <v>1529</v>
       </c>
       <c r="D331" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="E331" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
       <c r="F331" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="G331" t="s">
-        <v>1531</v>
+        <v>61</v>
       </c>
       <c r="H331">
-        <v>-31.573125352740586</v>
+        <v>-32.50637235957521</v>
       </c>
       <c r="I331">
-        <v>-68.52816662490439</v>
+        <v>-64.98560366393653</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B332" t="s">
         <v>57</v>
       </c>
       <c r="C332" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D332" t="s">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="E332" t="s">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="F332" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="G332" t="s">
-        <v>1537</v>
+        <v>61</v>
       </c>
       <c r="H332">
-        <v>-32.4107421</v>
+        <v>-33.282868169802846</v>
       </c>
       <c r="I332">
-        <v>-64.999353</v>
+        <v>-66.32257907646428</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="B333" t="s">
-        <v>57</v>
+        <v>1543</v>
       </c>
       <c r="C333" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D333" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
       <c r="E333" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="F333" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="G333" t="s">
-        <v>61</v>
+        <v>1547</v>
       </c>
       <c r="H333">
-        <v>-32.50637235957521</v>
+        <v>-33.18587233139957</v>
       </c>
       <c r="I333">
-        <v>-64.98560366393653</v>
+        <v>-66.30927143350756</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="B334" t="s">
         <v>57</v>
       </c>
       <c r="C334" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D334" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
       <c r="E334" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="F334" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="G334" t="s">
         <v>61</v>
       </c>
       <c r="H334">
-        <v>-33.282868169802846</v>
+        <v>-32.44005744764045</v>
       </c>
       <c r="I334">
-        <v>-66.32257907646428</v>
+        <v>-65.00373671961584</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="B335" t="s">
-        <v>1547</v>
+        <v>1334</v>
       </c>
       <c r="C335" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D335" t="s">
-        <v>1548</v>
+        <v>485</v>
       </c>
       <c r="E335" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="F335" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="G335" t="s">
-        <v>1551</v>
+        <v>61</v>
       </c>
       <c r="H335">
-        <v>-33.188058</v>
+        <v>-32.351903273835816</v>
       </c>
       <c r="I335">
-        <v>-66.3131842</v>
+        <v>-65.01624230471928</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="B336" t="s">
         <v>57</v>
       </c>
       <c r="C336" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D336" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="E336" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="F336" t="s">
-        <v>1555</v>
+        <v>61</v>
       </c>
       <c r="G336" t="s">
         <v>61</v>
       </c>
       <c r="H336">
-        <v>-32.4354127</v>
+        <v>-32.67444942455353</v>
       </c>
       <c r="I336">
-        <v>-65.0083569</v>
+        <v>-64.98918264680428</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B337" t="s">
-        <v>1403</v>
+        <v>1559</v>
       </c>
       <c r="C337" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D337" t="s">
-        <v>485</v>
+        <v>1529</v>
       </c>
       <c r="E337" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="F337" t="s">
-        <v>61</v>
+        <v>1561</v>
       </c>
       <c r="G337" t="s">
-        <v>61</v>
+        <v>1562</v>
       </c>
       <c r="H337">
-        <v>-32.3230977</v>
+        <v>-33.28223136541646</v>
       </c>
       <c r="I337">
-        <v>-65.0351135</v>
+        <v>-66.33591610234926</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="B338" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C338" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D338" t="s">
-        <v>1559</v>
+        <v>1529</v>
       </c>
       <c r="E338" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="F338" t="s">
-        <v>61</v>
+        <v>1565</v>
       </c>
       <c r="G338" t="s">
-        <v>61</v>
+        <v>1566</v>
       </c>
       <c r="H338">
-        <v>-32.6753403</v>
+        <v>-33.139818852165476</v>
       </c>
       <c r="I338">
-        <v>-64.9887669</v>
+        <v>-66.52004730667468</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="B339" t="s">
-        <v>1562</v>
+        <v>57</v>
       </c>
       <c r="C339" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D339" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="E339" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="F339" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G339" t="s">
         <v>61</v>
       </c>
-      <c r="G339" t="s">
-        <v>1564</v>
-      </c>
       <c r="H339">
-        <v>-33.28223136541646</v>
+        <v>-32.33746020919768</v>
       </c>
       <c r="I339">
-        <v>-66.33591610234926</v>
+        <v>-65.20820645683301</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="B340" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C340" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D340" t="s">
-        <v>1533</v>
+        <v>1572</v>
       </c>
       <c r="E340" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="F340" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="G340" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="H340">
-        <v>-33.1385127</v>
+        <v>-35.15469224562694</v>
       </c>
       <c r="I340">
-        <v>-66.5200498</v>
+        <v>-65.94514552434379</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="B341" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="C341" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D341" t="s">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="E341" t="s">
-        <v>1571</v>
+        <v>1578</v>
       </c>
       <c r="F341" t="s">
-        <v>1572</v>
+        <v>61</v>
       </c>
       <c r="G341" t="s">
         <v>61</v>
       </c>
       <c r="H341">
-        <v>-32.342821</v>
+        <v>-33.7042516</v>
       </c>
       <c r="I341">
-        <v>-65.208157</v>
+        <v>-65.4337419</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="B342" t="s">
-        <v>57</v>
+        <v>536</v>
       </c>
       <c r="C342" t="s">
-        <v>1533</v>
+        <v>1580</v>
       </c>
       <c r="D342" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
       <c r="E342" t="s">
-        <v>1575</v>
+        <v>1582</v>
       </c>
       <c r="F342" t="s">
-        <v>1576</v>
+        <v>1583</v>
       </c>
       <c r="G342" t="s">
-        <v>61</v>
+        <v>1584</v>
       </c>
       <c r="H342">
-        <v>-35.15468098393773</v>
+        <v>-50.33447036739715</v>
       </c>
       <c r="I342">
-        <v>-65.94513784462717</v>
+        <v>-72.23866604931995</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
       <c r="B343" t="s">
-        <v>193</v>
+        <v>1334</v>
       </c>
       <c r="C343" t="s">
-        <v>1533</v>
+        <v>1580</v>
       </c>
       <c r="D343" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="E343" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="F343" t="s">
-        <v>61</v>
+        <v>1588</v>
       </c>
       <c r="G343" t="s">
         <v>61</v>
       </c>
       <c r="H343">
-        <v>-33.7042516</v>
+        <v>-48.7549907</v>
       </c>
       <c r="I343">
-        <v>-65.4337419</v>
+        <v>-70.2452704</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B344" t="s">
+        <v>287</v>
+      </c>
+      <c r="C344" t="s">
         <v>1580</v>
       </c>
-      <c r="B344" t="s">
-        <v>536</v>
-      </c>
-      <c r="C344" t="s">
-        <v>1581</v>
-      </c>
       <c r="D344" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
       <c r="E344" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="F344" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="G344" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="H344">
-        <v>-50.3347615</v>
+        <v>-46.54934961199202</v>
       </c>
       <c r="I344">
-        <v>-72.2463137</v>
+        <v>-68.92259151540017</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
       <c r="B345" t="s">
-        <v>1403</v>
+        <v>35</v>
       </c>
       <c r="C345" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="D345" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="E345" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="F345" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="G345" t="s">
         <v>61</v>
       </c>
       <c r="H345">
-        <v>-48.7549907</v>
+        <v>-33.2404687</v>
       </c>
       <c r="I345">
-        <v>-70.2452704</v>
+        <v>-60.829703</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1590</v>
+        <v>402</v>
       </c>
       <c r="B346" t="s">
-        <v>287</v>
+        <v>35</v>
       </c>
       <c r="C346" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="D346" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="E346" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="F346" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
       <c r="G346" t="s">
         <v>61</v>
       </c>
       <c r="H346">
-        <v>-46.54934961199202</v>
+        <v>-33.1522446</v>
       </c>
       <c r="I346">
-        <v>-68.92259151540017</v>
+        <v>-60.5180135</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="B347" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C347" t="s">
         <v>1595</v>
       </c>
       <c r="D347" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="E347" t="s">
-        <v>1597</v>
+        <v>1604</v>
       </c>
       <c r="F347" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
       <c r="G347" t="s">
         <v>61</v>
       </c>
       <c r="H347">
-        <v>-33.2404687</v>
+        <v>-33.3746119</v>
       </c>
       <c r="I347">
-        <v>-60.829703</v>
+        <v>-61.1800554</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>402</v>
+        <v>1606</v>
       </c>
       <c r="B348" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C348" t="s">
         <v>1595</v>
       </c>
       <c r="D348" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="E348" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="F348" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="G348" t="s">
-        <v>61</v>
+        <v>1610</v>
       </c>
       <c r="H348">
-        <v>-33.1522446</v>
+        <v>-32.8193559</v>
       </c>
       <c r="I348">
-        <v>-60.5180135</v>
+        <v>-60.7121099</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="B349" t="s">
         <v>57</v>
@@ -16346,56 +16346,56 @@
         <v>1595</v>
       </c>
       <c r="D349" t="s">
-        <v>1603</v>
+        <v>1612</v>
       </c>
       <c r="E349" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="F349" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
       <c r="G349" t="s">
-        <v>61</v>
+        <v>1615</v>
       </c>
       <c r="H349">
-        <v>-33.3746119</v>
+        <v>-32.0474551</v>
       </c>
       <c r="I349">
-        <v>-61.1800554</v>
+        <v>-61.7844037</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1606</v>
+        <v>1616</v>
       </c>
       <c r="B350" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C350" t="s">
         <v>1595</v>
       </c>
       <c r="D350" t="s">
-        <v>1607</v>
+        <v>1617</v>
       </c>
       <c r="E350" t="s">
-        <v>1608</v>
+        <v>1618</v>
       </c>
       <c r="F350" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="G350" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="H350">
-        <v>-32.8193559</v>
+        <v>-33.0520296</v>
       </c>
       <c r="I350">
-        <v>-60.7121099</v>
+        <v>-61.182569</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
       <c r="B351" t="s">
         <v>57</v>
@@ -16404,27 +16404,27 @@
         <v>1595</v>
       </c>
       <c r="D351" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="E351" t="s">
-        <v>1613</v>
+        <v>1622</v>
       </c>
       <c r="F351" t="s">
-        <v>1614</v>
+        <v>1623</v>
       </c>
       <c r="G351" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="H351">
-        <v>-32.0474551</v>
+        <v>-33.03675969972988</v>
       </c>
       <c r="I351">
-        <v>-61.7844037</v>
+        <v>-61.15748377030632</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1616</v>
+        <v>1625</v>
       </c>
       <c r="B352" t="s">
         <v>35</v>
@@ -16433,27 +16433,27 @@
         <v>1595</v>
       </c>
       <c r="D352" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="E352" t="s">
-        <v>1618</v>
+        <v>1627</v>
       </c>
       <c r="F352" t="s">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="G352" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="H352">
-        <v>-33.0520296</v>
+        <v>-33.1844289</v>
       </c>
       <c r="I352">
-        <v>-61.182569</v>
+        <v>-60.721565</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="B353" t="s">
         <v>57</v>
@@ -16462,27 +16462,27 @@
         <v>1595</v>
       </c>
       <c r="D353" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
       <c r="E353" t="s">
-        <v>1622</v>
+        <v>1632</v>
       </c>
       <c r="F353" t="s">
-        <v>1623</v>
+        <v>1633</v>
       </c>
       <c r="G353" t="s">
-        <v>1624</v>
+        <v>1634</v>
       </c>
       <c r="H353">
-        <v>-33.03675969972988</v>
+        <v>-31.4422024</v>
       </c>
       <c r="I353">
-        <v>-61.15748377030632</v>
+        <v>-60.9361923</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1625</v>
+        <v>1635</v>
       </c>
       <c r="B354" t="s">
         <v>35</v>
@@ -16491,27 +16491,27 @@
         <v>1595</v>
       </c>
       <c r="D354" t="s">
-        <v>1626</v>
+        <v>1636</v>
       </c>
       <c r="E354" t="s">
-        <v>1627</v>
+        <v>1637</v>
       </c>
       <c r="F354" t="s">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="G354" t="s">
-        <v>1629</v>
+        <v>61</v>
       </c>
       <c r="H354">
-        <v>-33.1844289</v>
+        <v>-33.1970961</v>
       </c>
       <c r="I354">
-        <v>-60.721565</v>
+        <v>-60.4672236</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="B355" t="s">
         <v>57</v>
@@ -16520,56 +16520,56 @@
         <v>1595</v>
       </c>
       <c r="D355" t="s">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="E355" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="F355" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="G355" t="s">
-        <v>1634</v>
+        <v>61</v>
       </c>
       <c r="H355">
-        <v>-31.4422024</v>
+        <v>-32.9191693</v>
       </c>
       <c r="I355">
-        <v>-60.9361923</v>
+        <v>-60.8119118</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="B356" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C356" t="s">
         <v>1595</v>
       </c>
       <c r="D356" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="E356" t="s">
-        <v>1637</v>
+        <v>1644</v>
       </c>
       <c r="F356" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="G356" t="s">
         <v>61</v>
       </c>
       <c r="H356">
-        <v>-33.1970961</v>
+        <v>-32.9078186</v>
       </c>
       <c r="I356">
-        <v>-60.4672236</v>
+        <v>-60.8008635</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="B357" t="s">
         <v>57</v>
@@ -16578,27 +16578,27 @@
         <v>1595</v>
       </c>
       <c r="D357" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="E357" t="s">
-        <v>1641</v>
+        <v>1648</v>
       </c>
       <c r="F357" t="s">
-        <v>1642</v>
+        <v>1649</v>
       </c>
       <c r="G357" t="s">
-        <v>61</v>
+        <v>1650</v>
       </c>
       <c r="H357">
-        <v>-32.9191693</v>
+        <v>-32.8565921</v>
       </c>
       <c r="I357">
-        <v>-60.8119118</v>
+        <v>-60.704995</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
       <c r="B358" t="s">
         <v>57</v>
@@ -16607,27 +16607,27 @@
         <v>1595</v>
       </c>
       <c r="D358" t="s">
-        <v>1640</v>
+        <v>1652</v>
       </c>
       <c r="E358" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F358" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="G358" t="s">
-        <v>61</v>
+        <v>1655</v>
       </c>
       <c r="H358">
-        <v>-32.9078186</v>
+        <v>-32.6765879</v>
       </c>
       <c r="I358">
-        <v>-60.8008635</v>
+        <v>-61.5133955</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1646</v>
+        <v>1656</v>
       </c>
       <c r="B359" t="s">
         <v>57</v>
@@ -16636,56 +16636,56 @@
         <v>1595</v>
       </c>
       <c r="D359" t="s">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="E359" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="F359" t="s">
-        <v>1649</v>
+        <v>1659</v>
       </c>
       <c r="G359" t="s">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="H359">
-        <v>-32.8565921</v>
+        <v>-32.48028</v>
       </c>
       <c r="I359">
-        <v>-60.704995</v>
+        <v>-61.5815426</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1651</v>
+        <v>1661</v>
       </c>
       <c r="B360" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C360" t="s">
         <v>1595</v>
       </c>
       <c r="D360" t="s">
-        <v>1652</v>
+        <v>1662</v>
       </c>
       <c r="E360" t="s">
-        <v>1653</v>
+        <v>1663</v>
       </c>
       <c r="F360" t="s">
-        <v>1654</v>
+        <v>1664</v>
       </c>
       <c r="G360" t="s">
-        <v>1655</v>
+        <v>1665</v>
       </c>
       <c r="H360">
-        <v>-32.6765879</v>
+        <v>-28.3488598</v>
       </c>
       <c r="I360">
-        <v>-61.5133955</v>
+        <v>-59.2582375</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1656</v>
+        <v>1666</v>
       </c>
       <c r="B361" t="s">
         <v>57</v>
@@ -16694,201 +16694,201 @@
         <v>1595</v>
       </c>
       <c r="D361" t="s">
-        <v>1657</v>
+        <v>1667</v>
       </c>
       <c r="E361" t="s">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="F361" t="s">
-        <v>1659</v>
+        <v>1669</v>
       </c>
       <c r="G361" t="s">
-        <v>1660</v>
+        <v>1670</v>
       </c>
       <c r="H361">
-        <v>-32.48028</v>
+        <v>-32.4588967</v>
       </c>
       <c r="I361">
-        <v>-61.5815426</v>
+        <v>-60.8884349</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="B362" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C362" t="s">
         <v>1595</v>
       </c>
       <c r="D362" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
       <c r="E362" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="F362" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="G362" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="H362">
-        <v>-28.3488598</v>
+        <v>-31.6773941</v>
       </c>
       <c r="I362">
-        <v>-59.2582375</v>
+        <v>-61.7547481</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1666</v>
+        <v>1676</v>
       </c>
       <c r="B363" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C363" t="s">
         <v>1595</v>
       </c>
       <c r="D363" t="s">
-        <v>1667</v>
+        <v>1677</v>
       </c>
       <c r="E363" t="s">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="F363" t="s">
-        <v>1669</v>
+        <v>1679</v>
       </c>
       <c r="G363" t="s">
-        <v>1670</v>
+        <v>61</v>
       </c>
       <c r="H363">
-        <v>-32.4588967</v>
+        <v>-33.64592345563525</v>
       </c>
       <c r="I363">
-        <v>-60.8884349</v>
+        <v>-61.86032544311777</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1671</v>
+        <v>1680</v>
       </c>
       <c r="B364" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C364" t="s">
         <v>1595</v>
       </c>
       <c r="D364" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="E364" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="F364" t="s">
-        <v>1674</v>
+        <v>1683</v>
       </c>
       <c r="G364" t="s">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="H364">
-        <v>-31.6773941</v>
+        <v>-33.3109137</v>
       </c>
       <c r="I364">
-        <v>-61.7547481</v>
+        <v>-60.8271374</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="B365" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C365" t="s">
         <v>1595</v>
       </c>
       <c r="D365" t="s">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="E365" t="s">
-        <v>1678</v>
+        <v>1687</v>
       </c>
       <c r="F365" t="s">
-        <v>1679</v>
+        <v>1688</v>
       </c>
       <c r="G365" t="s">
-        <v>61</v>
+        <v>1689</v>
       </c>
       <c r="H365">
-        <v>-33.64592345563525</v>
+        <v>-31.2563261</v>
       </c>
       <c r="I365">
-        <v>-61.86032544311777</v>
+        <v>-61.4970574</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1680</v>
+        <v>1690</v>
       </c>
       <c r="B366" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C366" t="s">
         <v>1595</v>
       </c>
       <c r="D366" t="s">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="E366" t="s">
-        <v>1682</v>
+        <v>1691</v>
       </c>
       <c r="F366" t="s">
-        <v>1683</v>
+        <v>1692</v>
       </c>
       <c r="G366" t="s">
-        <v>1684</v>
+        <v>1693</v>
       </c>
       <c r="H366">
-        <v>-33.3109137</v>
+        <v>-31.2444802</v>
       </c>
       <c r="I366">
-        <v>-60.8271374</v>
+        <v>-61.501275</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1685</v>
+        <v>1694</v>
       </c>
       <c r="B367" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C367" t="s">
         <v>1595</v>
       </c>
       <c r="D367" t="s">
-        <v>1686</v>
+        <v>1695</v>
       </c>
       <c r="E367" t="s">
-        <v>1687</v>
+        <v>1696</v>
       </c>
       <c r="F367" t="s">
-        <v>1688</v>
+        <v>1697</v>
       </c>
       <c r="G367" t="s">
-        <v>1689</v>
+        <v>61</v>
       </c>
       <c r="H367">
-        <v>-31.2563261</v>
+        <v>-29.234007038547652</v>
       </c>
       <c r="I367">
-        <v>-61.4970574</v>
+        <v>-59.58082872074677</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="B368" t="s">
         <v>57</v>
@@ -16897,59 +16897,59 @@
         <v>1595</v>
       </c>
       <c r="D368" t="s">
-        <v>1686</v>
+        <v>1699</v>
       </c>
       <c r="E368" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="F368" t="s">
-        <v>1692</v>
+        <v>1701</v>
       </c>
       <c r="G368" t="s">
-        <v>1693</v>
+        <v>61</v>
       </c>
       <c r="H368">
-        <v>-31.2444802</v>
+        <v>-29.162464660933185</v>
       </c>
       <c r="I368">
-        <v>-61.501275</v>
+        <v>-59.67799994607922</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="B369" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C369" t="s">
         <v>1595</v>
       </c>
       <c r="D369" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="E369" t="s">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="F369" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="G369" t="s">
         <v>61</v>
       </c>
       <c r="H369">
-        <v>-29.234007038547652</v>
+        <v>-29.144619</v>
       </c>
       <c r="I369">
-        <v>-59.58082872074677</v>
+        <v>-59.642549</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="B370" t="s">
-        <v>57</v>
+        <v>1706</v>
       </c>
       <c r="C370" t="s">
         <v>1595</v>
@@ -16958,24 +16958,24 @@
         <v>1699</v>
       </c>
       <c r="E370" t="s">
-        <v>1700</v>
+        <v>1707</v>
       </c>
       <c r="F370" t="s">
-        <v>1701</v>
+        <v>1708</v>
       </c>
       <c r="G370" t="s">
-        <v>61</v>
+        <v>1709</v>
       </c>
       <c r="H370">
-        <v>-29.162464660933185</v>
+        <v>-29.1383262</v>
       </c>
       <c r="I370">
-        <v>-59.67799994607922</v>
+        <v>-59.6553973</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="B371" t="s">
         <v>57</v>
@@ -16987,143 +16987,143 @@
         <v>1699</v>
       </c>
       <c r="E371" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="F371" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="G371" t="s">
-        <v>61</v>
+        <v>1713</v>
       </c>
       <c r="H371">
-        <v>-29.144619</v>
+        <v>-29.1886312</v>
       </c>
       <c r="I371">
-        <v>-59.642549</v>
+        <v>-59.6842037</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="B372" t="s">
-        <v>1706</v>
+        <v>57</v>
       </c>
       <c r="C372" t="s">
         <v>1595</v>
       </c>
       <c r="D372" t="s">
-        <v>1699</v>
+        <v>1715</v>
       </c>
       <c r="E372" t="s">
-        <v>1707</v>
+        <v>1716</v>
       </c>
       <c r="F372" t="s">
-        <v>1708</v>
+        <v>1717</v>
       </c>
       <c r="G372" t="s">
-        <v>1709</v>
+        <v>1718</v>
       </c>
       <c r="H372">
-        <v>-29.1383262</v>
+        <v>-32.9010103</v>
       </c>
       <c r="I372">
-        <v>-59.6553973</v>
+        <v>-60.910487</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1710</v>
+        <v>1719</v>
       </c>
       <c r="B373" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C373" t="s">
         <v>1595</v>
       </c>
       <c r="D373" t="s">
-        <v>1699</v>
+        <v>1720</v>
       </c>
       <c r="E373" t="s">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="F373" t="s">
-        <v>1712</v>
+        <v>1722</v>
       </c>
       <c r="G373" t="s">
-        <v>1713</v>
+        <v>61</v>
       </c>
       <c r="H373">
-        <v>-29.1886312</v>
+        <v>-29.4983369</v>
       </c>
       <c r="I373">
-        <v>-59.6842037</v>
+        <v>-59.752056</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="B374" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C374" t="s">
         <v>1595</v>
       </c>
       <c r="D374" t="s">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="E374" t="s">
-        <v>1716</v>
+        <v>1725</v>
       </c>
       <c r="F374" t="s">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="G374" t="s">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="H374">
-        <v>-32.9010103</v>
+        <v>-32.9400671</v>
       </c>
       <c r="I374">
-        <v>-60.910487</v>
+        <v>-60.6637017</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="B375" t="s">
-        <v>35</v>
+        <v>1729</v>
       </c>
       <c r="C375" t="s">
         <v>1595</v>
       </c>
       <c r="D375" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E375" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="F375" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
       <c r="G375" t="s">
-        <v>61</v>
+        <v>1732</v>
       </c>
       <c r="H375">
-        <v>-29.4983369</v>
+        <v>-32.9464664</v>
       </c>
       <c r="I375">
-        <v>-59.752056</v>
+        <v>-60.6518642</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>1723</v>
+        <v>1733</v>
       </c>
       <c r="B376" t="s">
-        <v>35</v>
+        <v>1734</v>
       </c>
       <c r="C376" t="s">
         <v>1595</v>
@@ -17132,27 +17132,27 @@
         <v>1724</v>
       </c>
       <c r="E376" t="s">
-        <v>1725</v>
+        <v>1735</v>
       </c>
       <c r="F376" t="s">
-        <v>1726</v>
+        <v>1736</v>
       </c>
       <c r="G376" t="s">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="H376">
-        <v>-32.9400671</v>
+        <v>-32.9195828</v>
       </c>
       <c r="I376">
-        <v>-60.6637017</v>
+        <v>-60.6909359</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1728</v>
+        <v>1738</v>
       </c>
       <c r="B377" t="s">
-        <v>1729</v>
+        <v>287</v>
       </c>
       <c r="C377" t="s">
         <v>1595</v>
@@ -17161,27 +17161,27 @@
         <v>1724</v>
       </c>
       <c r="E377" t="s">
-        <v>1730</v>
+        <v>1739</v>
       </c>
       <c r="F377" t="s">
-        <v>1731</v>
+        <v>1740</v>
       </c>
       <c r="G377" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="H377">
-        <v>-32.9464664</v>
+        <v>-32.9123507</v>
       </c>
       <c r="I377">
-        <v>-60.6518642</v>
+        <v>-60.6819909</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1733</v>
+        <v>1742</v>
       </c>
       <c r="B378" t="s">
-        <v>1734</v>
+        <v>57</v>
       </c>
       <c r="C378" t="s">
         <v>1595</v>
@@ -17190,27 +17190,27 @@
         <v>1724</v>
       </c>
       <c r="E378" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="F378" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
       <c r="G378" t="s">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="H378">
-        <v>-32.9195828</v>
+        <v>-32.8948146</v>
       </c>
       <c r="I378">
-        <v>-60.6909359</v>
+        <v>-60.6904607</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>1738</v>
+        <v>1746</v>
       </c>
       <c r="B379" t="s">
-        <v>287</v>
+        <v>35</v>
       </c>
       <c r="C379" t="s">
         <v>1595</v>
@@ -17219,53 +17219,53 @@
         <v>1724</v>
       </c>
       <c r="E379" t="s">
-        <v>1739</v>
+        <v>1747</v>
       </c>
       <c r="F379" t="s">
-        <v>1740</v>
+        <v>1748</v>
       </c>
       <c r="G379" t="s">
-        <v>1741</v>
+        <v>61</v>
       </c>
       <c r="H379">
-        <v>-32.9123507</v>
+        <v>-32.9385417</v>
       </c>
       <c r="I379">
-        <v>-60.6819909</v>
+        <v>-60.6647429</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
       <c r="B380" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C380" t="s">
         <v>1595</v>
       </c>
       <c r="D380" t="s">
-        <v>1724</v>
+        <v>1750</v>
       </c>
       <c r="E380" t="s">
-        <v>1743</v>
+        <v>1751</v>
       </c>
       <c r="F380" t="s">
-        <v>1744</v>
+        <v>1752</v>
       </c>
       <c r="G380" t="s">
-        <v>1745</v>
+        <v>61</v>
       </c>
       <c r="H380">
-        <v>-32.8948146</v>
+        <v>-30.3526069</v>
       </c>
       <c r="I380">
-        <v>-60.6904607</v>
+        <v>-61.8999914</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>1746</v>
+        <v>1753</v>
       </c>
       <c r="B381" t="s">
         <v>35</v>
@@ -17274,27 +17274,27 @@
         <v>1595</v>
       </c>
       <c r="D381" t="s">
-        <v>1724</v>
+        <v>1750</v>
       </c>
       <c r="E381" t="s">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="F381" t="s">
-        <v>1748</v>
+        <v>1755</v>
       </c>
       <c r="G381" t="s">
-        <v>61</v>
+        <v>1756</v>
       </c>
       <c r="H381">
-        <v>-32.9385417</v>
+        <v>-30.3621045</v>
       </c>
       <c r="I381">
-        <v>-60.6647429</v>
+        <v>-61.912876</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1749</v>
+        <v>1514</v>
       </c>
       <c r="B382" t="s">
         <v>35</v>
@@ -17303,56 +17303,56 @@
         <v>1595</v>
       </c>
       <c r="D382" t="s">
-        <v>1750</v>
+        <v>1757</v>
       </c>
       <c r="E382" t="s">
-        <v>1751</v>
+        <v>1758</v>
       </c>
       <c r="F382" t="s">
-        <v>1752</v>
+        <v>1759</v>
       </c>
       <c r="G382" t="s">
         <v>61</v>
       </c>
       <c r="H382">
-        <v>-30.3526069</v>
+        <v>-30.583365992494688</v>
       </c>
       <c r="I382">
-        <v>-61.8999914</v>
+        <v>-59.93431745393157</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1753</v>
+        <v>1760</v>
       </c>
       <c r="B383" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C383" t="s">
         <v>1595</v>
       </c>
       <c r="D383" t="s">
-        <v>1750</v>
+        <v>1761</v>
       </c>
       <c r="E383" t="s">
-        <v>1754</v>
+        <v>1762</v>
       </c>
       <c r="F383" t="s">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="G383" t="s">
-        <v>1756</v>
+        <v>61</v>
       </c>
       <c r="H383">
-        <v>-30.3621045</v>
+        <v>-32.7874256</v>
       </c>
       <c r="I383">
-        <v>-61.912876</v>
+        <v>-60.7295083</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1516</v>
+        <v>1764</v>
       </c>
       <c r="B384" t="s">
         <v>35</v>
@@ -17361,27 +17361,27 @@
         <v>1595</v>
       </c>
       <c r="D384" t="s">
-        <v>1757</v>
+        <v>1595</v>
       </c>
       <c r="E384" t="s">
-        <v>1758</v>
+        <v>1765</v>
       </c>
       <c r="F384" t="s">
-        <v>1759</v>
+        <v>1766</v>
       </c>
       <c r="G384" t="s">
         <v>61</v>
       </c>
       <c r="H384">
-        <v>-30.583365992494688</v>
+        <v>-31.5894029</v>
       </c>
       <c r="I384">
-        <v>-59.93431745393157</v>
+        <v>-60.7323876</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>1760</v>
+        <v>1767</v>
       </c>
       <c r="B385" t="s">
         <v>57</v>
@@ -17390,30 +17390,30 @@
         <v>1595</v>
       </c>
       <c r="D385" t="s">
-        <v>1761</v>
+        <v>1595</v>
       </c>
       <c r="E385" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="F385" t="s">
-        <v>1763</v>
+        <v>61</v>
       </c>
       <c r="G385" t="s">
-        <v>61</v>
+        <v>1769</v>
       </c>
       <c r="H385">
-        <v>-32.7874256</v>
+        <v>-31.638915032834483</v>
       </c>
       <c r="I385">
-        <v>-60.7295083</v>
+        <v>-60.72884512124277</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="B386" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C386" t="s">
         <v>1595</v>
@@ -17422,27 +17422,27 @@
         <v>1595</v>
       </c>
       <c r="E386" t="s">
-        <v>1765</v>
+        <v>1771</v>
       </c>
       <c r="F386" t="s">
-        <v>1766</v>
+        <v>61</v>
       </c>
       <c r="G386" t="s">
         <v>61</v>
       </c>
       <c r="H386">
-        <v>-31.5894029</v>
+        <v>-31.5966456</v>
       </c>
       <c r="I386">
-        <v>-60.7323876</v>
+        <v>-60.7167914</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="B387" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C387" t="s">
         <v>1595</v>
@@ -17451,27 +17451,27 @@
         <v>1595</v>
       </c>
       <c r="E387" t="s">
-        <v>1768</v>
+        <v>1773</v>
       </c>
       <c r="F387" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G387" t="s">
         <v>61</v>
       </c>
-      <c r="G387" t="s">
-        <v>1769</v>
-      </c>
       <c r="H387">
-        <v>-31.638915032834483</v>
+        <v>-31.6074219</v>
       </c>
       <c r="I387">
-        <v>-60.72884512124277</v>
+        <v>-60.7125608</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="B388" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C388" t="s">
         <v>1595</v>
@@ -17480,27 +17480,27 @@
         <v>1595</v>
       </c>
       <c r="E388" t="s">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="F388" t="s">
-        <v>61</v>
+        <v>1777</v>
       </c>
       <c r="G388" t="s">
         <v>61</v>
       </c>
       <c r="H388">
-        <v>-31.5966456</v>
+        <v>-31.5563607</v>
       </c>
       <c r="I388">
-        <v>-60.7167914</v>
+        <v>-60.7283922</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>1772</v>
+        <v>1778</v>
       </c>
       <c r="B389" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C389" t="s">
         <v>1595</v>
@@ -17509,27 +17509,27 @@
         <v>1595</v>
       </c>
       <c r="E389" t="s">
-        <v>1773</v>
+        <v>1779</v>
       </c>
       <c r="F389" t="s">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="G389" t="s">
-        <v>61</v>
+        <v>1781</v>
       </c>
       <c r="H389">
-        <v>-31.6074219</v>
+        <v>-31.6501826</v>
       </c>
       <c r="I389">
-        <v>-60.7125608</v>
+        <v>-60.7056492</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>1775</v>
+        <v>1782</v>
       </c>
       <c r="B390" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C390" t="s">
         <v>1595</v>
@@ -17538,27 +17538,27 @@
         <v>1595</v>
       </c>
       <c r="E390" t="s">
-        <v>1776</v>
+        <v>1783</v>
       </c>
       <c r="F390" t="s">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="G390" t="s">
         <v>61</v>
       </c>
       <c r="H390">
-        <v>-31.5563607</v>
+        <v>-31.5848693</v>
       </c>
       <c r="I390">
-        <v>-60.7283922</v>
+        <v>-60.7347339</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>1778</v>
+        <v>1785</v>
       </c>
       <c r="B391" t="s">
-        <v>57</v>
+        <v>536</v>
       </c>
       <c r="C391" t="s">
         <v>1595</v>
@@ -17567,24 +17567,24 @@
         <v>1595</v>
       </c>
       <c r="E391" t="s">
-        <v>1779</v>
+        <v>1786</v>
       </c>
       <c r="F391" t="s">
-        <v>1780</v>
+        <v>1787</v>
       </c>
       <c r="G391" t="s">
-        <v>1781</v>
+        <v>1788</v>
       </c>
       <c r="H391">
-        <v>-31.6501826</v>
+        <v>-31.6450941</v>
       </c>
       <c r="I391">
-        <v>-60.7056492</v>
+        <v>-60.7279453</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>1782</v>
+        <v>1789</v>
       </c>
       <c r="B392" t="s">
         <v>57</v>
@@ -17596,53 +17596,53 @@
         <v>1595</v>
       </c>
       <c r="E392" t="s">
-        <v>1783</v>
+        <v>1790</v>
       </c>
       <c r="F392" t="s">
-        <v>1784</v>
+        <v>1791</v>
       </c>
       <c r="G392" t="s">
-        <v>61</v>
+        <v>1792</v>
       </c>
       <c r="H392">
-        <v>-31.5848693</v>
+        <v>-32.9213099</v>
       </c>
       <c r="I392">
-        <v>-60.7347339</v>
+        <v>-60.6957351</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>1785</v>
+        <v>1793</v>
       </c>
       <c r="B393" t="s">
-        <v>536</v>
+        <v>57</v>
       </c>
       <c r="C393" t="s">
         <v>1595</v>
       </c>
       <c r="D393" t="s">
-        <v>1595</v>
+        <v>1794</v>
       </c>
       <c r="E393" t="s">
-        <v>1786</v>
+        <v>1795</v>
       </c>
       <c r="F393" t="s">
-        <v>1787</v>
+        <v>1796</v>
       </c>
       <c r="G393" t="s">
-        <v>1788</v>
+        <v>1797</v>
       </c>
       <c r="H393">
-        <v>-31.6450941</v>
+        <v>-31.6662064</v>
       </c>
       <c r="I393">
-        <v>-60.7279453</v>
+        <v>-60.7684242</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1789</v>
+        <v>1798</v>
       </c>
       <c r="B394" t="s">
         <v>57</v>
@@ -17651,27 +17651,27 @@
         <v>1595</v>
       </c>
       <c r="D394" t="s">
-        <v>1595</v>
+        <v>1794</v>
       </c>
       <c r="E394" t="s">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="F394" t="s">
-        <v>1791</v>
+        <v>1800</v>
       </c>
       <c r="G394" t="s">
-        <v>1792</v>
+        <v>1801</v>
       </c>
       <c r="H394">
-        <v>-32.9213099</v>
+        <v>-31.6829741</v>
       </c>
       <c r="I394">
-        <v>-60.6957351</v>
+        <v>-60.7542645</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="B395" t="s">
         <v>57</v>
@@ -17680,27 +17680,27 @@
         <v>1595</v>
       </c>
       <c r="D395" t="s">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="E395" t="s">
-        <v>1795</v>
+        <v>1804</v>
       </c>
       <c r="F395" t="s">
-        <v>1796</v>
+        <v>1805</v>
       </c>
       <c r="G395" t="s">
-        <v>1797</v>
+        <v>61</v>
       </c>
       <c r="H395">
-        <v>-31.6662064</v>
+        <v>-31.701640271800375</v>
       </c>
       <c r="I395">
-        <v>-60.7684242</v>
+        <v>-60.762648472200354</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>1798</v>
+        <v>1806</v>
       </c>
       <c r="B396" t="s">
         <v>57</v>
@@ -17709,27 +17709,27 @@
         <v>1595</v>
       </c>
       <c r="D396" t="s">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="E396" t="s">
-        <v>1799</v>
+        <v>1807</v>
       </c>
       <c r="F396" t="s">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="G396" t="s">
-        <v>1801</v>
+        <v>61</v>
       </c>
       <c r="H396">
-        <v>-31.6829741</v>
+        <v>-31.7710819</v>
       </c>
       <c r="I396">
-        <v>-60.7542645</v>
+        <v>-60.836596</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>1802</v>
+        <v>1809</v>
       </c>
       <c r="B397" t="s">
         <v>57</v>
@@ -17741,24 +17741,24 @@
         <v>1803</v>
       </c>
       <c r="E397" t="s">
-        <v>1804</v>
+        <v>1810</v>
       </c>
       <c r="F397" t="s">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="G397" t="s">
         <v>61</v>
       </c>
       <c r="H397">
-        <v>-31.701640271800375</v>
+        <v>-31.7023586</v>
       </c>
       <c r="I397">
-        <v>-60.762648472200354</v>
+        <v>-60.7696428</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="B398" t="s">
         <v>57</v>
@@ -17767,27 +17767,27 @@
         <v>1595</v>
       </c>
       <c r="D398" t="s">
-        <v>1803</v>
+        <v>1813</v>
       </c>
       <c r="E398" t="s">
-        <v>1807</v>
+        <v>1814</v>
       </c>
       <c r="F398" t="s">
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="G398" t="s">
-        <v>61</v>
+        <v>1816</v>
       </c>
       <c r="H398">
-        <v>-31.7710819</v>
+        <v>-30.5365136</v>
       </c>
       <c r="I398">
-        <v>-60.836596</v>
+        <v>-61.9614783</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="B399" t="s">
         <v>57</v>
@@ -17796,27 +17796,27 @@
         <v>1595</v>
       </c>
       <c r="D399" t="s">
-        <v>1803</v>
+        <v>1818</v>
       </c>
       <c r="E399" t="s">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="F399" t="s">
-        <v>1811</v>
+        <v>1820</v>
       </c>
       <c r="G399" t="s">
-        <v>61</v>
+        <v>1821</v>
       </c>
       <c r="H399">
-        <v>-31.7023586</v>
+        <v>-34.1432104</v>
       </c>
       <c r="I399">
-        <v>-60.7696428</v>
+        <v>-61.4781279</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1812</v>
+        <v>1822</v>
       </c>
       <c r="B400" t="s">
         <v>57</v>
@@ -17825,27 +17825,27 @@
         <v>1595</v>
       </c>
       <c r="D400" t="s">
-        <v>1813</v>
+        <v>1823</v>
       </c>
       <c r="E400" t="s">
-        <v>1814</v>
+        <v>1824</v>
       </c>
       <c r="F400" t="s">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="G400" t="s">
-        <v>1816</v>
+        <v>61</v>
       </c>
       <c r="H400">
-        <v>-30.5365136</v>
+        <v>-29.23819364712673</v>
       </c>
       <c r="I400">
-        <v>-61.9614783</v>
+        <v>-61.77047646637991</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1817</v>
+        <v>1826</v>
       </c>
       <c r="B401" t="s">
         <v>57</v>
@@ -17854,27 +17854,27 @@
         <v>1595</v>
       </c>
       <c r="D401" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="E401" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
       <c r="F401" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="G401" t="s">
-        <v>1821</v>
+        <v>61</v>
       </c>
       <c r="H401">
-        <v>-34.1432104</v>
+        <v>-29.2155733</v>
       </c>
       <c r="I401">
-        <v>-61.4781279</v>
+        <v>-61.7684067</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1822</v>
+        <v>1828</v>
       </c>
       <c r="B402" t="s">
         <v>57</v>
@@ -17883,56 +17883,56 @@
         <v>1595</v>
       </c>
       <c r="D402" t="s">
-        <v>1823</v>
+        <v>1829</v>
       </c>
       <c r="E402" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="F402" t="s">
-        <v>1825</v>
+        <v>1831</v>
       </c>
       <c r="G402" t="s">
-        <v>61</v>
+        <v>1832</v>
       </c>
       <c r="H402">
-        <v>-29.23819364712673</v>
+        <v>-33.7590358</v>
       </c>
       <c r="I402">
-        <v>-61.77047646637991</v>
+        <v>-61.9419552</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1826</v>
+        <v>1833</v>
       </c>
       <c r="B403" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C403" t="s">
         <v>1595</v>
       </c>
       <c r="D403" t="s">
-        <v>1823</v>
+        <v>1834</v>
       </c>
       <c r="E403" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="F403" t="s">
-        <v>1825</v>
+        <v>1697</v>
       </c>
       <c r="G403" t="s">
         <v>61</v>
       </c>
       <c r="H403">
-        <v>-29.2155733</v>
+        <v>-29.45534</v>
       </c>
       <c r="I403">
-        <v>-61.7684067</v>
+        <v>-60.2209267</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
       <c r="B404" t="s">
         <v>57</v>
@@ -17941,27 +17941,27 @@
         <v>1595</v>
       </c>
       <c r="D404" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="E404" t="s">
-        <v>1830</v>
+        <v>1838</v>
       </c>
       <c r="F404" t="s">
-        <v>1831</v>
+        <v>1839</v>
       </c>
       <c r="G404" t="s">
-        <v>1832</v>
+        <v>1840</v>
       </c>
       <c r="H404">
-        <v>-33.7590358</v>
+        <v>-32.03644704437168</v>
       </c>
       <c r="I404">
-        <v>-61.9419552</v>
+        <v>-61.229698082291115</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="B405" t="s">
         <v>35</v>
@@ -17970,30 +17970,30 @@
         <v>1595</v>
       </c>
       <c r="D405" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="E405" t="s">
-        <v>1835</v>
+        <v>1842</v>
       </c>
       <c r="F405" t="s">
-        <v>1697</v>
+        <v>1843</v>
       </c>
       <c r="G405" t="s">
         <v>61</v>
       </c>
       <c r="H405">
-        <v>-29.45534</v>
+        <v>-33.025917780865</v>
       </c>
       <c r="I405">
-        <v>-60.2209267</v>
+        <v>-60.64796334956165</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1836</v>
+        <v>1061</v>
       </c>
       <c r="B406" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C406" t="s">
         <v>1595</v>
@@ -18002,27 +18002,27 @@
         <v>1837</v>
       </c>
       <c r="E406" t="s">
-        <v>1838</v>
+        <v>1844</v>
       </c>
       <c r="F406" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="G406" t="s">
-        <v>1840</v>
+        <v>61</v>
       </c>
       <c r="H406">
-        <v>-32.03644704437168</v>
+        <v>-33.036264</v>
       </c>
       <c r="I406">
-        <v>-61.229698082291115</v>
+        <v>-60.6539489</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="B407" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C407" t="s">
         <v>1595</v>
@@ -18031,24 +18031,24 @@
         <v>1837</v>
       </c>
       <c r="E407" t="s">
-        <v>1842</v>
+        <v>1847</v>
       </c>
       <c r="F407" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
       <c r="G407" t="s">
-        <v>61</v>
+        <v>1849</v>
       </c>
       <c r="H407">
-        <v>-33.025917780865</v>
+        <v>-33.0236385</v>
       </c>
       <c r="I407">
-        <v>-60.64796334956165</v>
+        <v>-60.6310782</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1061</v>
+        <v>1850</v>
       </c>
       <c r="B408" t="s">
         <v>35</v>
@@ -18060,172 +18060,172 @@
         <v>1837</v>
       </c>
       <c r="E408" t="s">
-        <v>1844</v>
+        <v>1851</v>
       </c>
       <c r="F408" t="s">
-        <v>1845</v>
+        <v>1852</v>
       </c>
       <c r="G408" t="s">
-        <v>61</v>
+        <v>1853</v>
       </c>
       <c r="H408">
-        <v>-33.036264</v>
+        <v>-32.017977081171324</v>
       </c>
       <c r="I408">
-        <v>-60.6539489</v>
+        <v>-61.226588872381484</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>1846</v>
+        <v>1854</v>
       </c>
       <c r="B409" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C409" t="s">
         <v>1595</v>
       </c>
       <c r="D409" t="s">
-        <v>1837</v>
+        <v>1855</v>
       </c>
       <c r="E409" t="s">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="F409" t="s">
-        <v>1848</v>
+        <v>1857</v>
       </c>
       <c r="G409" t="s">
-        <v>1849</v>
+        <v>61</v>
       </c>
       <c r="H409">
-        <v>-33.0236385</v>
+        <v>-28.4952245</v>
       </c>
       <c r="I409">
-        <v>-60.6310782</v>
+        <v>-59.3540046</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B410" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C410" t="s">
         <v>1595</v>
       </c>
       <c r="D410" t="s">
-        <v>1837</v>
+        <v>1855</v>
       </c>
       <c r="E410" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="F410" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="G410" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="H410">
-        <v>-32.017977081171324</v>
+        <v>-28.49985</v>
       </c>
       <c r="I410">
-        <v>-61.226588872381484</v>
+        <v>-59.3498885</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="B411" t="s">
-        <v>35</v>
+        <v>979</v>
       </c>
       <c r="C411" t="s">
-        <v>1595</v>
+        <v>1863</v>
       </c>
       <c r="D411" t="s">
-        <v>1855</v>
+        <v>1864</v>
       </c>
       <c r="E411" t="s">
-        <v>1856</v>
+        <v>1865</v>
       </c>
       <c r="F411" t="s">
-        <v>1857</v>
+        <v>1866</v>
       </c>
       <c r="G411" t="s">
         <v>61</v>
       </c>
       <c r="H411">
-        <v>-28.4952245</v>
+        <v>-27.722554390777788</v>
       </c>
       <c r="I411">
-        <v>-59.3540046</v>
+        <v>-64.22118130088897</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>1858</v>
+        <v>1867</v>
       </c>
       <c r="B412" t="s">
-        <v>57</v>
+        <v>1868</v>
       </c>
       <c r="C412" t="s">
-        <v>1595</v>
+        <v>1863</v>
       </c>
       <c r="D412" t="s">
-        <v>1855</v>
+        <v>1863</v>
       </c>
       <c r="E412" t="s">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="F412" t="s">
-        <v>1860</v>
+        <v>1870</v>
       </c>
       <c r="G412" t="s">
-        <v>1861</v>
+        <v>1871</v>
       </c>
       <c r="H412">
-        <v>-28.49985</v>
+        <v>-27.7792666</v>
       </c>
       <c r="I412">
-        <v>-59.3498885</v>
+        <v>-64.2733716</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>1862</v>
+        <v>1872</v>
       </c>
       <c r="B413" t="s">
-        <v>979</v>
+        <v>1873</v>
       </c>
       <c r="C413" t="s">
         <v>1863</v>
       </c>
       <c r="D413" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E413" t="s">
-        <v>1865</v>
+        <v>1874</v>
       </c>
       <c r="F413" t="s">
-        <v>1866</v>
+        <v>1875</v>
       </c>
       <c r="G413" t="s">
-        <v>61</v>
+        <v>1876</v>
       </c>
       <c r="H413">
-        <v>-27.7273118</v>
+        <v>-27.7795196</v>
       </c>
       <c r="I413">
-        <v>-64.2295706</v>
+        <v>-64.2718455</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="B414" t="s">
-        <v>1868</v>
+        <v>57</v>
       </c>
       <c r="C414" t="s">
         <v>1863</v>
@@ -18234,111 +18234,111 @@
         <v>1863</v>
       </c>
       <c r="E414" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="F414" t="s">
-        <v>1870</v>
+        <v>1879</v>
       </c>
       <c r="G414" t="s">
-        <v>1871</v>
+        <v>1880</v>
       </c>
       <c r="H414">
-        <v>-27.7792666</v>
+        <v>-27.79407699388719</v>
       </c>
       <c r="I414">
-        <v>-64.2733716</v>
+        <v>-64.296509648456</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>1872</v>
+        <v>1881</v>
       </c>
       <c r="B415" t="s">
-        <v>1873</v>
+        <v>35</v>
       </c>
       <c r="C415" t="s">
-        <v>1863</v>
+        <v>1882</v>
       </c>
       <c r="D415" t="s">
-        <v>1863</v>
+        <v>1883</v>
       </c>
       <c r="E415" t="s">
-        <v>1874</v>
+        <v>1884</v>
       </c>
       <c r="F415" t="s">
-        <v>1875</v>
+        <v>1885</v>
       </c>
       <c r="G415" t="s">
-        <v>1876</v>
+        <v>1886</v>
       </c>
       <c r="H415">
-        <v>-27.7795196</v>
+        <v>-51.69218657548685</v>
       </c>
       <c r="I415">
-        <v>-64.2718455</v>
+        <v>-57.86855876700162</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>1877</v>
+        <v>1887</v>
       </c>
       <c r="B416" t="s">
-        <v>57</v>
+        <v>1888</v>
       </c>
       <c r="C416" t="s">
-        <v>1863</v>
+        <v>1882</v>
       </c>
       <c r="D416" t="s">
-        <v>1863</v>
+        <v>1889</v>
       </c>
       <c r="E416" t="s">
-        <v>1878</v>
+        <v>1890</v>
       </c>
       <c r="F416" t="s">
-        <v>1879</v>
+        <v>1891</v>
       </c>
       <c r="G416" t="s">
-        <v>1880</v>
+        <v>61</v>
       </c>
       <c r="H416">
-        <v>-27.7962673</v>
+        <v>-53.7694225</v>
       </c>
       <c r="I416">
-        <v>-64.2957388</v>
+        <v>-67.731218</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>1881</v>
+        <v>1892</v>
       </c>
       <c r="B417" t="s">
-        <v>35</v>
+        <v>1893</v>
       </c>
       <c r="C417" t="s">
         <v>1882</v>
       </c>
       <c r="D417" t="s">
-        <v>1883</v>
+        <v>1889</v>
       </c>
       <c r="E417" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
       <c r="F417" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="G417" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="H417">
-        <v>-51.69218657548685</v>
+        <v>-53.802672272422484</v>
       </c>
       <c r="I417">
-        <v>-57.86855876700162</v>
+        <v>-67.66017098860993</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="B418" t="s">
         <v>1888</v>
@@ -18350,27 +18350,27 @@
         <v>1889</v>
       </c>
       <c r="E418" t="s">
-        <v>1890</v>
+        <v>1898</v>
       </c>
       <c r="F418" t="s">
-        <v>1891</v>
+        <v>1899</v>
       </c>
       <c r="G418" t="s">
-        <v>61</v>
+        <v>1900</v>
       </c>
       <c r="H418">
-        <v>-53.7694225</v>
+        <v>-53.80752627242417</v>
       </c>
       <c r="I418">
-        <v>-67.731218</v>
+        <v>-67.6768389309388</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>1892</v>
+        <v>1901</v>
       </c>
       <c r="B419" t="s">
-        <v>1893</v>
+        <v>241</v>
       </c>
       <c r="C419" t="s">
         <v>1882</v>
@@ -18379,53 +18379,53 @@
         <v>1889</v>
       </c>
       <c r="E419" t="s">
-        <v>1894</v>
+        <v>1902</v>
       </c>
       <c r="F419" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
       <c r="G419" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="H419">
-        <v>-53.802672272422484</v>
+        <v>-53.7821237</v>
       </c>
       <c r="I419">
-        <v>-67.66017098860993</v>
+        <v>-67.6989925</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>1897</v>
+        <v>1905</v>
       </c>
       <c r="B420" t="s">
-        <v>1888</v>
+        <v>1906</v>
       </c>
       <c r="C420" t="s">
         <v>1882</v>
       </c>
       <c r="D420" t="s">
-        <v>1889</v>
+        <v>1907</v>
       </c>
       <c r="E420" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="F420" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="G420" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="H420">
-        <v>-53.80752627242417</v>
+        <v>-54.51056188613015</v>
       </c>
       <c r="I420">
-        <v>-67.6768389309388</v>
+        <v>-67.19492653090096</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>1901</v>
+        <v>646</v>
       </c>
       <c r="B421" t="s">
         <v>241</v>
@@ -18434,175 +18434,175 @@
         <v>1882</v>
       </c>
       <c r="D421" t="s">
-        <v>1889</v>
+        <v>1911</v>
       </c>
       <c r="E421" t="s">
-        <v>1902</v>
+        <v>1912</v>
       </c>
       <c r="F421" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
       <c r="G421" t="s">
-        <v>1904</v>
+        <v>1914</v>
       </c>
       <c r="H421">
-        <v>-53.7821237</v>
+        <v>-54.8024469</v>
       </c>
       <c r="I421">
-        <v>-67.6989925</v>
+        <v>-68.3140352</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="B422" t="s">
-        <v>1906</v>
+        <v>979</v>
       </c>
       <c r="C422" t="s">
         <v>1882</v>
       </c>
       <c r="D422" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="E422" t="s">
-        <v>1908</v>
+        <v>1916</v>
       </c>
       <c r="F422" t="s">
-        <v>1909</v>
+        <v>1917</v>
       </c>
       <c r="G422" t="s">
-        <v>1910</v>
+        <v>61</v>
       </c>
       <c r="H422">
-        <v>-54.51056188613015</v>
+        <v>-54.81373287202315</v>
       </c>
       <c r="I422">
-        <v>-67.19492653090096</v>
+        <v>-68.32357290346708</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>646</v>
+        <v>1918</v>
       </c>
       <c r="B423" t="s">
-        <v>241</v>
+        <v>817</v>
       </c>
       <c r="C423" t="s">
-        <v>1882</v>
+        <v>1919</v>
       </c>
       <c r="D423" t="s">
-        <v>1911</v>
+        <v>1920</v>
       </c>
       <c r="E423" t="s">
-        <v>1912</v>
+        <v>1921</v>
       </c>
       <c r="F423" t="s">
-        <v>1913</v>
+        <v>1922</v>
       </c>
       <c r="G423" t="s">
-        <v>1914</v>
+        <v>61</v>
       </c>
       <c r="H423">
-        <v>-54.8024469</v>
+        <v>-27.3454217</v>
       </c>
       <c r="I423">
-        <v>-68.3140352</v>
+        <v>-65.6043219</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
       <c r="B424" t="s">
-        <v>979</v>
+        <v>1729</v>
       </c>
       <c r="C424" t="s">
-        <v>1882</v>
+        <v>1919</v>
       </c>
       <c r="D424" t="s">
-        <v>1911</v>
+        <v>1924</v>
       </c>
       <c r="E424" t="s">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="F424" t="s">
-        <v>1917</v>
+        <v>1926</v>
       </c>
       <c r="G424" t="s">
-        <v>61</v>
+        <v>1927</v>
       </c>
       <c r="H424">
-        <v>-54.81373287202315</v>
+        <v>-26.9294351</v>
       </c>
       <c r="I424">
-        <v>-68.32357290346708</v>
+        <v>-65.3387446</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>1918</v>
+        <v>1928</v>
       </c>
       <c r="B425" t="s">
-        <v>817</v>
+        <v>1334</v>
       </c>
       <c r="C425" t="s">
         <v>1919</v>
       </c>
       <c r="D425" t="s">
-        <v>1920</v>
+        <v>1929</v>
       </c>
       <c r="E425" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="F425" t="s">
-        <v>1922</v>
+        <v>1931</v>
       </c>
       <c r="G425" t="s">
-        <v>61</v>
+        <v>1932</v>
       </c>
       <c r="H425">
-        <v>-27.3454217</v>
+        <v>-26.834956669197283</v>
       </c>
       <c r="I425">
-        <v>-65.6043219</v>
+        <v>-65.26826458869172</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>1923</v>
+        <v>1933</v>
       </c>
       <c r="B426" t="s">
-        <v>1729</v>
+        <v>1934</v>
       </c>
       <c r="C426" t="s">
         <v>1919</v>
       </c>
       <c r="D426" t="s">
-        <v>1924</v>
+        <v>1929</v>
       </c>
       <c r="E426" t="s">
-        <v>1925</v>
+        <v>1935</v>
       </c>
       <c r="F426" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="G426" t="s">
-        <v>1927</v>
+        <v>61</v>
       </c>
       <c r="H426">
-        <v>-26.9294351</v>
+        <v>-26.8111212</v>
       </c>
       <c r="I426">
-        <v>-65.3387446</v>
+        <v>-65.1918714</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>1928</v>
+        <v>1937</v>
       </c>
       <c r="B427" t="s">
-        <v>1403</v>
+        <v>757</v>
       </c>
       <c r="C427" t="s">
         <v>1919</v>
@@ -18611,27 +18611,27 @@
         <v>1929</v>
       </c>
       <c r="E427" t="s">
-        <v>1930</v>
+        <v>1938</v>
       </c>
       <c r="F427" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
       <c r="G427" t="s">
-        <v>1932</v>
+        <v>61</v>
       </c>
       <c r="H427">
-        <v>-26.8111212</v>
+        <v>-26.79591501672503</v>
       </c>
       <c r="I427">
-        <v>-65.1918714</v>
+        <v>-65.19840073110994</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>1933</v>
+        <v>1940</v>
       </c>
       <c r="B428" t="s">
-        <v>1934</v>
+        <v>1868</v>
       </c>
       <c r="C428" t="s">
         <v>1919</v>
@@ -18640,76 +18640,18 @@
         <v>1929</v>
       </c>
       <c r="E428" t="s">
-        <v>1935</v>
+        <v>1941</v>
       </c>
       <c r="F428" t="s">
-        <v>1936</v>
+        <v>1942</v>
       </c>
       <c r="G428" t="s">
-        <v>61</v>
+        <v>1943</v>
       </c>
       <c r="H428">
-        <v>-26.8111212</v>
+        <v>-26.83607921998982</v>
       </c>
       <c r="I428">
-        <v>-65.1918714</v>
-      </c>
-    </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B429" t="s">
-        <v>757</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D429" t="s">
-        <v>1929</v>
-      </c>
-      <c r="E429" t="s">
-        <v>1938</v>
-      </c>
-      <c r="F429" t="s">
-        <v>1939</v>
-      </c>
-      <c r="G429" t="s">
-        <v>61</v>
-      </c>
-      <c r="H429">
-        <v>-26.79591501672503</v>
-      </c>
-      <c r="I429">
-        <v>-65.19840073110994</v>
-      </c>
-    </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
-        <v>1940</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C430" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D430" t="s">
-        <v>1929</v>
-      </c>
-      <c r="E430" t="s">
-        <v>1941</v>
-      </c>
-      <c r="F430" t="s">
-        <v>1942</v>
-      </c>
-      <c r="G430" t="s">
-        <v>1943</v>
-      </c>
-      <c r="H430">
-        <v>-26.83607921998982</v>
-      </c>
-      <c r="I430">
         <v>-65.20683638905523</v>
       </c>
     </row>
